--- a/Расписание.xlsx
+++ b/Расписание.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7470" windowHeight="2700" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="7470" windowHeight="2700" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="ПОНЕДЕЛЬНИК" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="248">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -61,6 +61,9 @@
     <t>5 пара</t>
   </si>
   <si>
+    <t>2 пара</t>
+  </si>
+  <si>
     <t>6 пара</t>
   </si>
   <si>
@@ -68,9 +71,6 @@
   </si>
   <si>
     <t>Физика/419</t>
-  </si>
-  <si>
-    <t>Классный час</t>
   </si>
   <si>
     <t>Математика/416</t>
@@ -100,6 +100,8 @@
         <sz val="17"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
       </rPr>
       <t>104</t>
     </r>
@@ -109,6 +111,8 @@
         <sz val="16"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
       </rPr>
       <t>эм</t>
     </r>
@@ -186,6 +190,9 @@
     <t>Измер.техн./308</t>
   </si>
   <si>
+    <t>Литература/233</t>
+  </si>
+  <si>
     <t>Инж.граф./421</t>
   </si>
   <si>
@@ -210,9 +217,6 @@
     <t>175т</t>
   </si>
   <si>
-    <t>Иностран. язык/312/314</t>
-  </si>
-  <si>
     <t>Иностр.яз./316</t>
   </si>
   <si>
@@ -402,9 +406,6 @@
     <t>Материаловед./357</t>
   </si>
   <si>
-    <t>ПМ 01/308</t>
-  </si>
-  <si>
     <t>Метеорология/201</t>
   </si>
   <si>
@@ -649,6 +650,150 @@
   </si>
   <si>
     <t>Понедельник</t>
+  </si>
+  <si>
+    <t>Классный час /104</t>
+  </si>
+  <si>
+    <t>Русский язык/233</t>
+  </si>
+  <si>
+    <t>Классный час /318</t>
+  </si>
+  <si>
+    <t>Классный час /233</t>
+  </si>
+  <si>
+    <t>Классный час /301</t>
+  </si>
+  <si>
+    <t>Классный час /405</t>
+  </si>
+  <si>
+    <t>Классный час /400</t>
+  </si>
+  <si>
+    <t>Классный час /300</t>
+  </si>
+  <si>
+    <t>Классный час /317</t>
+  </si>
+  <si>
+    <t>Классный час /421</t>
+  </si>
+  <si>
+    <t>Классный час /406</t>
+  </si>
+  <si>
+    <t>Классный час /308</t>
+  </si>
+  <si>
+    <t>Ин. язык/312/314</t>
+  </si>
+  <si>
+    <t>Классный час /401</t>
+  </si>
+  <si>
+    <t>Классный час /201</t>
+  </si>
+  <si>
+    <t>Классный час /327</t>
+  </si>
+  <si>
+    <t>Классный час / 312</t>
+  </si>
+  <si>
+    <t>Классный час / 404</t>
+  </si>
+  <si>
+    <t>Классный час / 318</t>
+  </si>
+  <si>
+    <t>Классный час /411</t>
+  </si>
+  <si>
+    <t>Классный час /423</t>
+  </si>
+  <si>
+    <t>Классный час /419</t>
+  </si>
+  <si>
+    <t>Классный час /416</t>
+  </si>
+  <si>
+    <t>Классный час /418</t>
+  </si>
+  <si>
+    <t>Классный час /312</t>
+  </si>
+  <si>
+    <t>Материалов./104</t>
+  </si>
+  <si>
+    <t>Классный час /228</t>
+  </si>
+  <si>
+    <t>Классный час /310</t>
+  </si>
+  <si>
+    <t>Классный час /231</t>
+  </si>
+  <si>
+    <t>Классный час /227</t>
+  </si>
+  <si>
+    <t>Классный час /304</t>
+  </si>
+  <si>
+    <t>Классный час /404</t>
+  </si>
+  <si>
+    <t>Обществозн/411</t>
+  </si>
+  <si>
+    <t>Проект.деят/327</t>
+  </si>
+  <si>
+    <t>Иностран. язык/312</t>
+  </si>
+  <si>
+    <t>Охрана труда/318</t>
+  </si>
+  <si>
+    <t>Материалов./317</t>
+  </si>
+  <si>
+    <t>Ин. яз/312/314</t>
+  </si>
+  <si>
+    <t>Культура речи/404</t>
+  </si>
+  <si>
+    <t>Материалов./411</t>
+  </si>
+  <si>
+    <t>Осн. фин. гр/418</t>
+  </si>
+  <si>
+    <t>ПМ05/305</t>
+  </si>
+  <si>
+    <t>Осн. экон/418</t>
+  </si>
+  <si>
+    <t>Психология/404</t>
+  </si>
+  <si>
+    <t>Физика/104</t>
+  </si>
+  <si>
+    <t>ПМ 01/300(М)</t>
+  </si>
+  <si>
+    <t>ПМ 03/414</t>
+  </si>
+  <si>
+    <t>ПМ 02/300(М)</t>
   </si>
 </sst>
 </file>
@@ -658,11 +803,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d\.m\.yyyy"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -671,22 +824,30 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
@@ -694,6 +855,8 @@
       <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
@@ -701,12 +864,16 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="17"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
@@ -718,23 +885,31 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color rgb="FF1F1F1F"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
@@ -746,12 +921,16 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
@@ -763,11 +942,15 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="13"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
@@ -779,6 +962,8 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
@@ -791,20 +976,35 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -841,8 +1041,14 @@
         <bgColor theme="0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -902,133 +1108,245 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1256,10 +1574,9 @@
     <col min="2" max="2" width="38.85546875" customWidth="1"/>
     <col min="3" max="3" width="38.28515625" customWidth="1"/>
     <col min="4" max="4" width="39.85546875" customWidth="1"/>
-    <col min="5" max="5" width="39.28515625" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" customWidth="1"/>
+    <col min="7" max="8" width="15" customWidth="1"/>
     <col min="9" max="11" width="8.7109375" customWidth="1"/>
     <col min="12" max="12" width="27" customWidth="1"/>
     <col min="13" max="13" width="15" customWidth="1"/>
@@ -1272,10 +1589,10 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56" t="s">
-        <v>200</v>
-      </c>
-      <c r="C1" s="55"/>
+      <c r="B1" s="73" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1" s="74"/>
       <c r="D1" s="5">
         <v>46265</v>
       </c>
@@ -1303,12 +1620,12 @@
         <v>9</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="26.25" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1426,7 +1743,7 @@
     </row>
     <row r="11" spans="1:15" ht="26.25" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
@@ -1441,7 +1758,7 @@
     </row>
     <row r="12" spans="1:15" ht="27" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -1456,7 +1773,7 @@
     </row>
     <row r="13" spans="1:15" ht="27" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -1466,7 +1783,7 @@
       <c r="G13" s="22"/>
       <c r="L13" s="28"/>
       <c r="O13" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="26.25" customHeight="1">
@@ -1481,7 +1798,7 @@
       <c r="G14" s="22"/>
       <c r="L14" s="28"/>
       <c r="O14" s="18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="27" customHeight="1">
@@ -1496,7 +1813,7 @@
       <c r="G15" s="22"/>
       <c r="L15" s="31"/>
       <c r="O15" s="18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="26.25" customHeight="1">
@@ -1786,7 +2103,7 @@
     </row>
     <row r="35" spans="1:35" ht="26.25" customHeight="1">
       <c r="A35" s="36" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B35" s="22"/>
       <c r="C35" s="15"/>
@@ -1801,7 +2118,7 @@
     </row>
     <row r="36" spans="1:35" ht="25.5" customHeight="1">
       <c r="A36" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="15"/>
@@ -1842,7 +2159,7 @@
     </row>
     <row r="37" spans="1:35" ht="15.75" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="15"/>
@@ -1857,7 +2174,7 @@
     </row>
     <row r="38" spans="1:35" ht="15.75" customHeight="1">
       <c r="A38" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="15"/>
@@ -1872,7 +2189,7 @@
     </row>
     <row r="39" spans="1:35" ht="15.75" customHeight="1">
       <c r="A39" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="15"/>
@@ -1887,7 +2204,7 @@
     </row>
     <row r="40" spans="1:35" ht="15.75" customHeight="1">
       <c r="A40" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B40" s="16"/>
       <c r="C40" s="15"/>
@@ -1902,7 +2219,7 @@
     </row>
     <row r="41" spans="1:35" ht="15.75" customHeight="1">
       <c r="A41" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B41" s="16"/>
       <c r="C41" s="15"/>
@@ -1924,17 +2241,17 @@
     <row r="43" spans="1:35" ht="15.75" customHeight="1">
       <c r="L43" s="31"/>
       <c r="O43" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" spans="1:35" ht="15.75" customHeight="1">
       <c r="O44" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:35" ht="15.75" customHeight="1">
       <c r="O45" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:35" ht="15.75" customHeight="1">
@@ -1946,19 +2263,19 @@
     <row r="47" spans="1:35" ht="15.75" customHeight="1">
       <c r="L47" s="24"/>
       <c r="O47" s="18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:35" ht="15.75" customHeight="1">
       <c r="L48" s="24"/>
       <c r="O48" s="18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="12:15" ht="15.75" customHeight="1">
       <c r="L49" s="39"/>
       <c r="O49" s="18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50" spans="12:15" ht="15.75" customHeight="1">
@@ -1970,49 +2287,49 @@
     <row r="51" spans="12:15" ht="15.75" customHeight="1">
       <c r="L51" s="39"/>
       <c r="O51" s="18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="12:15" ht="15.75" customHeight="1">
       <c r="L52" s="24"/>
       <c r="O52" s="18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="12:15" ht="15.75" customHeight="1">
       <c r="L53" s="24"/>
       <c r="O53" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54" spans="12:15" ht="15.75" customHeight="1">
       <c r="L54" s="24"/>
       <c r="O54" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="12:15" ht="15.75" customHeight="1">
       <c r="L55" s="39"/>
       <c r="O55" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="12:15" ht="15.75" customHeight="1">
       <c r="L56" s="39"/>
       <c r="O56" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="12:15" ht="15.75" customHeight="1">
       <c r="L57" s="24"/>
       <c r="O57" s="18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="12:15" ht="15.75" customHeight="1">
       <c r="L58" s="24"/>
       <c r="O58" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="12:15" ht="15.75" customHeight="1">
@@ -2030,208 +2347,208 @@
     <row r="61" spans="12:15" ht="15.75" customHeight="1">
       <c r="L61" s="24"/>
       <c r="O61" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="12:15" ht="15.75" customHeight="1">
       <c r="L62" s="24"/>
       <c r="O62" s="18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="12:15" ht="15.75" customHeight="1">
       <c r="L63" s="24"/>
       <c r="O63" s="18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="64" spans="12:15" ht="15.75" customHeight="1">
       <c r="L64" s="24"/>
       <c r="O64" s="18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="12:15" ht="15.75" customHeight="1">
       <c r="L65" s="24"/>
       <c r="O65" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="12:15" ht="15.75" customHeight="1">
       <c r="L66" s="24"/>
       <c r="O66" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="67" spans="12:15" ht="15.75" customHeight="1">
       <c r="L67" s="24"/>
       <c r="O67" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="68" spans="12:15" ht="15.75" customHeight="1">
       <c r="L68" s="24"/>
       <c r="O68" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69" spans="12:15" ht="15.75" customHeight="1">
       <c r="L69" s="24"/>
       <c r="O69" s="18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="12:15" ht="15.75" customHeight="1">
       <c r="L70" s="24"/>
       <c r="O70" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="71" spans="12:15" ht="15.75" customHeight="1">
       <c r="L71" s="24"/>
       <c r="O71" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="12:15" ht="15.75" customHeight="1">
       <c r="L72" s="24"/>
       <c r="O72" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73" spans="12:15" ht="15.75" customHeight="1">
       <c r="L73" s="24"/>
       <c r="O73" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="74" spans="12:15" ht="15.75" customHeight="1">
       <c r="L74" s="24"/>
       <c r="O74" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="75" spans="12:15" ht="15.75" customHeight="1">
       <c r="L75" s="24"/>
       <c r="O75" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="76" spans="12:15" ht="15.75" customHeight="1">
       <c r="L76" s="24"/>
       <c r="O76" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="77" spans="12:15" ht="15.75" customHeight="1">
       <c r="L77" s="24"/>
       <c r="O77" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="78" spans="12:15" ht="15.75" customHeight="1">
       <c r="L78" s="24"/>
       <c r="O78" s="18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="79" spans="12:15" ht="15.75" customHeight="1">
       <c r="L79" s="24"/>
       <c r="O79" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="80" spans="12:15" ht="15.75" customHeight="1">
       <c r="L80" s="24"/>
       <c r="O80" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="81" spans="12:15" ht="15.75" customHeight="1">
       <c r="L81" s="24"/>
       <c r="O81" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="82" spans="12:15" ht="15.75" customHeight="1">
       <c r="L82" s="24"/>
       <c r="O82" s="18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="83" spans="12:15" ht="15.75" customHeight="1">
       <c r="O83" s="18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="84" spans="12:15" ht="15.75" customHeight="1">
       <c r="O84" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="85" spans="12:15" ht="15.75" customHeight="1">
       <c r="O85" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="86" spans="12:15" ht="15.75" customHeight="1">
       <c r="O86" s="18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="87" spans="12:15" ht="15.75" customHeight="1">
       <c r="O87" s="18" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="88" spans="12:15" ht="15.75" customHeight="1">
       <c r="O88" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="89" spans="12:15" ht="15.75" customHeight="1">
       <c r="O89" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="90" spans="12:15" ht="15.75" customHeight="1">
       <c r="O90" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="91" spans="12:15" ht="15.75" customHeight="1">
       <c r="O91" s="18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="92" spans="12:15" ht="15.75" customHeight="1">
       <c r="O92" s="18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="93" spans="12:15" ht="15.75" customHeight="1">
       <c r="O93" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="94" spans="12:15" ht="15.75" customHeight="1">
       <c r="O94" s="18" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="95" spans="12:15" ht="15.75" customHeight="1">
       <c r="O95" s="18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="96" spans="12:15" ht="15.75" customHeight="1">
       <c r="O96" s="18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="97" spans="12:15" ht="15.75" customHeight="1">
       <c r="O97" s="18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="98" spans="12:15" ht="15.75" customHeight="1">
@@ -2252,7 +2569,7 @@
     <row r="101" spans="12:15" ht="15.75" customHeight="1">
       <c r="L101" s="23"/>
       <c r="O101" s="18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="102" spans="12:15" ht="15.75" customHeight="1">
@@ -2264,7 +2581,7 @@
     <row r="103" spans="12:15" ht="15.75" customHeight="1">
       <c r="L103" s="24"/>
       <c r="O103" s="18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="104" spans="12:15" ht="15.75" customHeight="1">
@@ -2282,7 +2599,7 @@
     <row r="106" spans="12:15" ht="15.75" customHeight="1">
       <c r="L106" s="39"/>
       <c r="O106" s="18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107" spans="12:15" ht="15.75" customHeight="1">
@@ -2294,7 +2611,7 @@
     <row r="108" spans="12:15" ht="15.75" customHeight="1">
       <c r="L108" s="39"/>
       <c r="O108" s="18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="109" spans="12:15" ht="15.75" customHeight="1">
@@ -2306,13 +2623,13 @@
     <row r="110" spans="12:15" ht="15.75" customHeight="1">
       <c r="L110" s="24"/>
       <c r="O110" s="18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="111" spans="12:15" ht="15.75" customHeight="1">
       <c r="L111" s="24"/>
       <c r="O111" s="18" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="112" spans="12:15" ht="15.75" customHeight="1">
@@ -2324,43 +2641,43 @@
     <row r="113" spans="12:15" ht="15.75" customHeight="1">
       <c r="L113" s="39"/>
       <c r="O113" s="18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="114" spans="12:15" ht="15.75" customHeight="1">
       <c r="L114" s="39"/>
       <c r="O114" s="18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="115" spans="12:15" ht="15.75" customHeight="1">
       <c r="L115" s="39"/>
       <c r="O115" s="18" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="116" spans="12:15" ht="15.75" customHeight="1">
       <c r="L116" s="24"/>
       <c r="O116" s="18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="117" spans="12:15" ht="15.75" customHeight="1">
       <c r="L117" s="24"/>
       <c r="O117" s="18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="118" spans="12:15" ht="15.75" customHeight="1">
       <c r="L118" s="39"/>
       <c r="O118" s="18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="119" spans="12:15" ht="15.75" customHeight="1">
       <c r="L119" s="39"/>
       <c r="O119" s="18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="120" spans="12:15" ht="15.75" customHeight="1">
@@ -2372,43 +2689,43 @@
     <row r="121" spans="12:15" ht="15.75" customHeight="1">
       <c r="L121" s="24"/>
       <c r="O121" s="18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="122" spans="12:15" ht="15.75" customHeight="1">
       <c r="L122" s="24"/>
       <c r="O122" s="18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="123" spans="12:15" ht="15.75" customHeight="1">
       <c r="L123" s="24"/>
       <c r="O123" s="18" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="124" spans="12:15" ht="15.75" customHeight="1">
       <c r="L124" s="24"/>
       <c r="O124" s="18" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="125" spans="12:15" ht="15.75" customHeight="1">
       <c r="L125" s="24"/>
       <c r="O125" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="126" spans="12:15" ht="15.75" customHeight="1">
       <c r="L126" s="24"/>
       <c r="O126" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="127" spans="12:15" ht="15.75" customHeight="1">
       <c r="L127" s="39"/>
       <c r="O127" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="128" spans="12:15" ht="15.75" customHeight="1">
@@ -3458,10 +3775,10 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56" t="s">
+      <c r="B1" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="55"/>
+      <c r="C1" s="74"/>
       <c r="D1" s="5">
         <v>46266</v>
       </c>
@@ -3469,7 +3786,7 @@
       <c r="F1" s="10"/>
       <c r="G1" s="13"/>
     </row>
-    <row r="2" spans="1:18" ht="22.5" customHeight="1">
+    <row r="2" spans="1:18" ht="22.5" customHeight="1" thickBot="1">
       <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
@@ -3489,311 +3806,311 @@
         <v>9</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="26.25" customHeight="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="26.25" customHeight="1" thickBot="1">
       <c r="A3" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="56" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" s="57" t="s">
+        <v>201</v>
+      </c>
+      <c r="D3" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="16"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="21"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
       <c r="R3" s="18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="26.25" customHeight="1">
+    <row r="4" spans="1:18" ht="26.25" customHeight="1" thickBot="1">
       <c r="A4" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="16" t="s">
+      <c r="B4" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="C4" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="16"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="21"/>
+      <c r="D4" s="61" t="s">
+        <v>201</v>
+      </c>
+      <c r="E4" s="62"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
       <c r="R4" s="18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="26.25" customHeight="1">
+    <row r="5" spans="1:18" ht="26.25" customHeight="1" thickBot="1">
       <c r="A5" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="16" t="s">
+      <c r="B5" s="60" t="s">
+        <v>203</v>
+      </c>
+      <c r="C5" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="22"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
       <c r="R5" s="18" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="26.25" customHeight="1">
+    <row r="6" spans="1:18" ht="26.25" customHeight="1" thickBot="1">
       <c r="A6" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="16" t="s">
+      <c r="B6" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="22"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
       <c r="R6" s="18" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="26.25" customHeight="1">
+    <row r="7" spans="1:18" ht="26.25" customHeight="1" thickBot="1">
       <c r="A7" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="16" t="s">
+      <c r="B7" s="60" t="s">
+        <v>205</v>
+      </c>
+      <c r="C7" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="61" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="22"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
       <c r="R7" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="26.25" customHeight="1">
+    <row r="8" spans="1:18" ht="26.25" customHeight="1" thickBot="1">
       <c r="A8" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="16" t="s">
+      <c r="B8" s="60" t="s">
+        <v>206</v>
+      </c>
+      <c r="C8" s="61" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="22"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
       <c r="R8" s="18" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="26.25" customHeight="1">
+    <row r="9" spans="1:18" ht="26.25" customHeight="1" thickBot="1">
       <c r="A9" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="16" t="s">
+      <c r="B9" s="60" t="s">
+        <v>207</v>
+      </c>
+      <c r="C9" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="22"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
       <c r="M9" s="23"/>
       <c r="R9" s="18" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="27.75" customHeight="1">
+    <row r="10" spans="1:18" ht="27.75" customHeight="1" thickBot="1">
       <c r="A10" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="16" t="s">
+      <c r="B10" s="60" t="s">
+        <v>208</v>
+      </c>
+      <c r="C10" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="30"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
       <c r="M10" s="24"/>
       <c r="R10" s="18" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="26.25" customHeight="1">
+    <row r="11" spans="1:18" ht="26.25" customHeight="1" thickBot="1">
       <c r="A11" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="60" t="s">
+        <v>209</v>
+      </c>
+      <c r="C11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="22"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
       <c r="M11" s="24"/>
       <c r="R11" s="18" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="27" customHeight="1">
+    <row r="12" spans="1:18" ht="27" customHeight="1" thickBot="1">
       <c r="A12" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="60" t="s">
+        <v>210</v>
+      </c>
+      <c r="C12" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="22"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="62"/>
       <c r="M12" s="28"/>
       <c r="R12" s="18" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="25.5" customHeight="1">
+    <row r="13" spans="1:18" ht="25.5" customHeight="1" thickBot="1">
       <c r="A13" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="B13" s="60" t="s">
+        <v>211</v>
+      </c>
+      <c r="C13" s="61" t="s">
+        <v>212</v>
+      </c>
+      <c r="D13" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="22"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
       <c r="M13" s="28"/>
       <c r="R13" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="23.25" customHeight="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="23.25" customHeight="1" thickBot="1">
       <c r="A14" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="16" t="s">
+      <c r="B14" s="60" t="s">
+        <v>213</v>
+      </c>
+      <c r="C14" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="15"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="22"/>
+      <c r="D14" s="61" t="s">
+        <v>212</v>
+      </c>
+      <c r="E14" s="64"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
       <c r="M14" s="28"/>
       <c r="R14" s="18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="28.5" customHeight="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="28.5" customHeight="1" thickBot="1">
       <c r="A15" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="14" t="s">
+      <c r="B15" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="C15" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="22"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
       <c r="M15" s="31"/>
       <c r="R15" s="18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="29.25" customHeight="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="29.25" customHeight="1" thickBot="1">
       <c r="A16" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="14" t="s">
+      <c r="B16" s="60" t="s">
+        <v>215</v>
+      </c>
+      <c r="C16" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="15"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="64"/>
+      <c r="G16" s="64"/>
       <c r="M16" s="31"/>
       <c r="R16" s="18" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="26.25" customHeight="1">
+    <row r="17" spans="1:18" ht="26.25" customHeight="1" thickBot="1">
       <c r="A17" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="14" t="s">
+      <c r="B17" s="66"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="61" t="s">
+        <v>216</v>
+      </c>
+      <c r="F17" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="65" t="s">
         <v>66</v>
       </c>
       <c r="M17" s="31"/>
@@ -3801,20 +4118,20 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="28.5" customHeight="1">
+    <row r="18" spans="1:18" ht="28.5" customHeight="1" thickBot="1">
       <c r="A18" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="14" t="s">
+      <c r="B18" s="66"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="61" t="s">
+        <v>217</v>
+      </c>
+      <c r="F18" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="65" t="s">
         <v>15</v>
       </c>
       <c r="M18" s="28"/>
@@ -3822,20 +4139,20 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="26.25" customHeight="1">
+    <row r="19" spans="1:18" ht="26.25" customHeight="1" thickBot="1">
       <c r="A19" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="14" t="s">
+      <c r="B19" s="66"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="61" t="s">
+        <v>218</v>
+      </c>
+      <c r="F19" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G19" s="65" t="s">
         <v>69</v>
       </c>
       <c r="M19" s="28"/>
@@ -3843,20 +4160,20 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="26.25" customHeight="1">
+    <row r="20" spans="1:18" ht="26.25" customHeight="1" thickBot="1">
       <c r="A20" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="G20" s="14" t="s">
+      <c r="B20" s="67"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="F20" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="G20" s="65" t="s">
         <v>75</v>
       </c>
       <c r="M20" s="31"/>
@@ -3864,41 +4181,41 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="26.25" customHeight="1">
+    <row r="21" spans="1:18" ht="26.25" customHeight="1" thickBot="1">
       <c r="A21" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="14" t="s">
+      <c r="B21" s="67"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="61" t="s">
+        <v>219</v>
+      </c>
+      <c r="F21" s="65" t="s">
         <v>75</v>
       </c>
-      <c r="G21" s="14" t="s">
-        <v>49</v>
+      <c r="G21" s="65" t="s">
+        <v>50</v>
       </c>
       <c r="M21" s="31"/>
       <c r="R21" s="18" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="26.25" customHeight="1">
+    <row r="22" spans="1:18" ht="26.25" customHeight="1" thickBot="1">
       <c r="A22" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="14" t="s">
+      <c r="B22" s="66"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="61" t="s">
+        <v>220</v>
+      </c>
+      <c r="F22" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="65" t="s">
         <v>80</v>
       </c>
       <c r="M22" s="28"/>
@@ -3906,20 +4223,20 @@
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="28.5" customHeight="1">
+    <row r="23" spans="1:18" ht="28.5" customHeight="1" thickBot="1">
       <c r="A23" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="14" t="s">
+      <c r="B23" s="66"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="61" t="s">
+        <v>221</v>
+      </c>
+      <c r="F23" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="65" t="s">
         <v>19</v>
       </c>
       <c r="M23" s="31"/>
@@ -3927,20 +4244,20 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="29.25" customHeight="1">
+    <row r="24" spans="1:18" ht="29.25" customHeight="1" thickBot="1">
       <c r="A24" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="14" t="s">
+      <c r="B24" s="66"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="61" t="s">
+        <v>222</v>
+      </c>
+      <c r="F24" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="G24" s="14" t="s">
+      <c r="G24" s="65" t="s">
         <v>32</v>
       </c>
       <c r="M24" s="28"/>
@@ -3948,62 +4265,62 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="29.25" customHeight="1">
+    <row r="25" spans="1:18" ht="29.25" customHeight="1" thickBot="1">
       <c r="A25" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="14" t="s">
+      <c r="B25" s="60" t="s">
+        <v>223</v>
+      </c>
+      <c r="C25" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="G25" s="14" t="s">
-        <v>89</v>
-      </c>
+      <c r="D25" s="65" t="s">
+        <v>188</v>
+      </c>
+      <c r="E25" s="62"/>
+      <c r="F25" s="64"/>
+      <c r="G25" s="64"/>
       <c r="M25" s="28"/>
       <c r="R25" s="18" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="26.25" customHeight="1">
+    <row r="26" spans="1:18" ht="26.25" customHeight="1" thickBot="1">
       <c r="A26" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="G26" s="14" t="s">
+      <c r="B26" s="60" t="s">
+        <v>224</v>
+      </c>
+      <c r="C26" s="65" t="s">
+        <v>188</v>
+      </c>
+      <c r="D26" s="65" t="s">
         <v>88</v>
       </c>
+      <c r="E26" s="62"/>
+      <c r="F26" s="64"/>
+      <c r="G26" s="64"/>
       <c r="M26" s="31"/>
       <c r="R26" s="18" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="26.25" customHeight="1">
+    <row r="27" spans="1:18" ht="26.25" customHeight="1" thickBot="1">
       <c r="A27" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="G27" s="14" t="s">
+      <c r="B27" s="66"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="F27" s="65" t="s">
+        <v>225</v>
+      </c>
+      <c r="G27" s="65" t="s">
         <v>95</v>
       </c>
       <c r="M27" s="31"/>
@@ -4011,20 +4328,20 @@
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="26.25" customHeight="1">
+    <row r="28" spans="1:18" ht="26.25" customHeight="1" thickBot="1">
       <c r="A28" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="14" t="s">
+      <c r="B28" s="66"/>
+      <c r="C28" s="64"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="61" t="s">
+        <v>226</v>
+      </c>
+      <c r="F28" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="15" t="s">
+      <c r="G28" s="65" t="s">
         <v>97</v>
       </c>
       <c r="M28" s="31"/>
@@ -4032,20 +4349,20 @@
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="26.25" customHeight="1">
+    <row r="29" spans="1:18" ht="26.25" customHeight="1" thickBot="1">
       <c r="A29" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" s="22" t="s">
+      <c r="B29" s="67"/>
+      <c r="C29" s="64"/>
+      <c r="D29" s="64"/>
+      <c r="E29" s="61" t="s">
+        <v>227</v>
+      </c>
+      <c r="F29" s="61" t="s">
         <v>100</v>
       </c>
-      <c r="G29" s="22" t="s">
+      <c r="G29" s="61" t="s">
         <v>101</v>
       </c>
       <c r="M29" s="28"/>
@@ -4053,20 +4370,20 @@
         <v>93</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="27" customHeight="1">
+    <row r="30" spans="1:18" ht="27" customHeight="1" thickBot="1">
       <c r="A30" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="22"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="22" t="s">
+      <c r="B30" s="67"/>
+      <c r="C30" s="64"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="61" t="s">
+        <v>228</v>
+      </c>
+      <c r="F30" s="61" t="s">
         <v>101</v>
       </c>
-      <c r="G30" s="22" t="s">
+      <c r="G30" s="61" t="s">
         <v>100</v>
       </c>
       <c r="M30" s="31"/>
@@ -4074,20 +4391,20 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="26.25" customHeight="1">
+    <row r="31" spans="1:18" ht="26.25" customHeight="1" thickBot="1">
       <c r="A31" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="15" t="s">
+      <c r="B31" s="67"/>
+      <c r="C31" s="64"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="61" t="s">
+        <v>229</v>
+      </c>
+      <c r="F31" s="65" t="s">
         <v>106</v>
       </c>
-      <c r="G31" s="15" t="s">
+      <c r="G31" s="65" t="s">
         <v>107</v>
       </c>
       <c r="M31" s="28"/>
@@ -4095,20 +4412,20 @@
         <v>99</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="26.25" customHeight="1">
+    <row r="32" spans="1:18" ht="26.25" customHeight="1" thickBot="1">
       <c r="A32" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="B32" s="22"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="15" t="s">
+      <c r="B32" s="67"/>
+      <c r="C32" s="64"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="61" t="s">
+        <v>207</v>
+      </c>
+      <c r="F32" s="65" t="s">
         <v>107</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="65" t="s">
         <v>106</v>
       </c>
       <c r="M32" s="28"/>
@@ -4116,20 +4433,20 @@
         <v>103</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="27.75" customHeight="1">
+    <row r="33" spans="1:18" ht="27.75" customHeight="1" thickBot="1">
       <c r="A33" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B33" s="22"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="15" t="s">
+      <c r="B33" s="67"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="61" t="s">
+        <v>209</v>
+      </c>
+      <c r="F33" s="65" t="s">
         <v>112</v>
       </c>
-      <c r="G33" s="15" t="s">
+      <c r="G33" s="65" t="s">
         <v>114</v>
       </c>
       <c r="M33" s="31"/>
@@ -4137,41 +4454,41 @@
         <v>105</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="26.25" customHeight="1">
+    <row r="34" spans="1:18" ht="26.25" customHeight="1" thickBot="1">
       <c r="A34" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="B34" s="22"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="32" t="s">
-        <v>118</v>
-      </c>
-      <c r="G34" s="32" t="s">
-        <v>118</v>
+      <c r="B34" s="67"/>
+      <c r="C34" s="64"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="61" t="s">
+        <v>210</v>
+      </c>
+      <c r="F34" s="65" t="s">
+        <v>140</v>
+      </c>
+      <c r="G34" s="65" t="s">
+        <v>140</v>
       </c>
       <c r="M34" s="24"/>
       <c r="R34" s="18" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="26.25" customHeight="1">
+    <row r="35" spans="1:18" ht="26.25" customHeight="1" thickBot="1">
       <c r="A35" s="36" t="s">
-        <v>122</v>
-      </c>
-      <c r="B35" s="22"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="32" t="s">
-        <v>127</v>
-      </c>
-      <c r="G35" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B35" s="67"/>
+      <c r="C35" s="64"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="61" t="s">
+        <v>215</v>
+      </c>
+      <c r="F35" s="65" t="s">
+        <v>126</v>
+      </c>
+      <c r="G35" s="65" t="s">
         <v>112</v>
       </c>
       <c r="M35" s="24"/>
@@ -4179,142 +4496,142 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="24.75" customHeight="1">
+    <row r="36" spans="1:18" ht="24.75" customHeight="1" thickBot="1">
       <c r="A36" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B36" s="60" t="s">
+        <v>206</v>
+      </c>
+      <c r="C36" s="65" t="s">
+        <v>133</v>
+      </c>
+      <c r="D36" s="65" t="s">
         <v>134</v>
       </c>
-      <c r="D36" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="E36" s="40"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="41"/>
+      <c r="E36" s="62"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="68"/>
       <c r="M36" s="24"/>
       <c r="R36" s="18" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="15.75" customHeight="1">
+    <row r="37" spans="1:18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A37" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="B37" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="E37" s="17"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
+        <v>137</v>
+      </c>
+      <c r="B37" s="60" t="s">
+        <v>230</v>
+      </c>
+      <c r="C37" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="D37" s="65" t="s">
+        <v>133</v>
+      </c>
+      <c r="E37" s="62"/>
+      <c r="F37" s="64"/>
+      <c r="G37" s="64"/>
       <c r="M37" s="37"/>
       <c r="R37" s="18" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="15.75" customHeight="1">
+    <row r="38" spans="1:18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A38" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="B38" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D38" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="B38" s="60" t="s">
+        <v>231</v>
+      </c>
+      <c r="C38" s="65" t="s">
         <v>134</v>
       </c>
-      <c r="E38" s="17"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
+      <c r="D38" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="E38" s="62"/>
+      <c r="F38" s="64"/>
+      <c r="G38" s="64"/>
       <c r="M38" s="31"/>
       <c r="R38" s="18" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="15.75" customHeight="1">
+    <row r="39" spans="1:18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A39" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="B39" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="B39" s="60" t="s">
+        <v>222</v>
+      </c>
+      <c r="C39" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="D39" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
+      <c r="D39" s="65" t="s">
+        <v>136</v>
+      </c>
+      <c r="E39" s="64"/>
+      <c r="F39" s="64"/>
+      <c r="G39" s="64"/>
       <c r="M39" s="31"/>
       <c r="R39" s="18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="15.75" customHeight="1">
+    <row r="40" spans="1:18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A40" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="D40" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="B40" s="60" t="s">
+        <v>220</v>
+      </c>
+      <c r="C40" s="65" t="s">
+        <v>136</v>
+      </c>
+      <c r="D40" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="E40" s="17"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="64"/>
       <c r="J40" s="43"/>
       <c r="M40" s="31"/>
       <c r="R40" s="18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="15.75" customHeight="1">
+    <row r="41" spans="1:18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A41" s="36" t="s">
-        <v>177</v>
-      </c>
-      <c r="B41" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="E41" s="35"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
+        <v>176</v>
+      </c>
+      <c r="B41" s="60" t="s">
+        <v>213</v>
+      </c>
+      <c r="C41" s="65" t="s">
+        <v>154</v>
+      </c>
+      <c r="D41" s="65" t="s">
+        <v>154</v>
+      </c>
+      <c r="E41" s="64"/>
+      <c r="F41" s="69"/>
+      <c r="G41" s="69"/>
       <c r="J41" s="43"/>
       <c r="M41" s="31"/>
       <c r="R41" s="18" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="15.75" customHeight="1">
+    <row r="42" spans="1:18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A42" s="36"/>
-      <c r="B42" s="16"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="40"/>
-      <c r="F42" s="41"/>
-      <c r="G42" s="41"/>
+      <c r="B42" s="67"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="62"/>
+      <c r="F42" s="68"/>
+      <c r="G42" s="68"/>
       <c r="J42" s="43"/>
       <c r="M42" s="28"/>
       <c r="R42" s="18" t="s">
@@ -4325,21 +4642,21 @@
       <c r="J43" s="43"/>
       <c r="M43" s="28"/>
       <c r="R43" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" spans="1:18" ht="15.75" customHeight="1">
       <c r="J44" s="43"/>
       <c r="M44" s="31"/>
       <c r="R44" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:18" ht="15.75" customHeight="1">
       <c r="J45" s="43"/>
       <c r="M45" s="31"/>
       <c r="R45" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:18" ht="15.75" customHeight="1">
@@ -4353,21 +4670,21 @@
       <c r="J47" s="43"/>
       <c r="M47" s="24"/>
       <c r="R47" s="18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="15.75" customHeight="1">
       <c r="J48" s="43"/>
       <c r="M48" s="24"/>
       <c r="R48" s="18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="10:18" ht="15.75" customHeight="1">
       <c r="J49" s="43"/>
       <c r="M49" s="39"/>
       <c r="R49" s="18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50" spans="10:18" ht="15.75" customHeight="1">
@@ -4381,56 +4698,56 @@
       <c r="J51" s="43"/>
       <c r="M51" s="39"/>
       <c r="R51" s="18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="10:18" ht="15.75" customHeight="1">
       <c r="J52" s="43"/>
       <c r="M52" s="24"/>
       <c r="R52" s="18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="10:18" ht="15.75" customHeight="1">
       <c r="J53" s="43"/>
       <c r="M53" s="24"/>
       <c r="R53" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54" spans="10:18" ht="15.75" customHeight="1">
       <c r="J54" s="43"/>
       <c r="M54" s="24"/>
       <c r="R54" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="10:18" ht="15.75" customHeight="1">
       <c r="J55" s="43"/>
       <c r="M55" s="39"/>
       <c r="R55" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="10:18" ht="15.75" customHeight="1">
       <c r="J56" s="43"/>
       <c r="M56" s="39"/>
       <c r="R56" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="10:18" ht="15.75" customHeight="1">
       <c r="J57" s="43"/>
       <c r="M57" s="24"/>
       <c r="R57" s="18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="10:18" ht="15.75" customHeight="1">
       <c r="J58" s="43"/>
       <c r="M58" s="24"/>
       <c r="R58" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="10:18" ht="15.75" customHeight="1">
@@ -4451,241 +4768,241 @@
       <c r="J61" s="43"/>
       <c r="M61" s="24"/>
       <c r="R61" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="10:18" ht="15.75" customHeight="1">
       <c r="J62" s="43"/>
       <c r="M62" s="24"/>
       <c r="R62" s="18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="10:18" ht="15.75" customHeight="1">
       <c r="J63" s="43"/>
       <c r="M63" s="24"/>
       <c r="R63" s="18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="64" spans="10:18" ht="15.75" customHeight="1">
       <c r="J64" s="43"/>
       <c r="M64" s="24"/>
       <c r="R64" s="18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="8:18" ht="15.75" customHeight="1">
       <c r="J65" s="43"/>
       <c r="M65" s="24"/>
       <c r="R65" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="8:18" ht="15.75" customHeight="1">
       <c r="J66" s="43"/>
       <c r="M66" s="24"/>
       <c r="R66" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="67" spans="8:18" ht="15.75" customHeight="1">
       <c r="M67" s="24"/>
       <c r="R67" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="68" spans="8:18" ht="15.75" customHeight="1">
       <c r="M68" s="24"/>
       <c r="R68" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69" spans="8:18" ht="15.75" customHeight="1">
       <c r="M69" s="24"/>
       <c r="R69" s="18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="8:18" ht="15.75" customHeight="1">
       <c r="H70" s="43"/>
       <c r="M70" s="24"/>
       <c r="R70" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="71" spans="8:18" ht="15.75" customHeight="1">
       <c r="H71" s="43"/>
       <c r="M71" s="24"/>
       <c r="R71" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="8:18" ht="15.75" customHeight="1">
       <c r="H72" s="43"/>
       <c r="M72" s="24"/>
       <c r="R72" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73" spans="8:18" ht="15.75" customHeight="1">
       <c r="H73" s="43"/>
       <c r="M73" s="24"/>
       <c r="R73" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="74" spans="8:18" ht="15.75" customHeight="1">
       <c r="H74" s="43"/>
       <c r="M74" s="24"/>
       <c r="R74" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="75" spans="8:18" ht="15.75" customHeight="1">
       <c r="H75" s="43"/>
       <c r="M75" s="24"/>
       <c r="R75" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="76" spans="8:18" ht="15.75" customHeight="1">
       <c r="H76" s="43"/>
       <c r="M76" s="24"/>
       <c r="R76" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="77" spans="8:18" ht="15.75" customHeight="1">
       <c r="H77" s="43"/>
       <c r="M77" s="24"/>
       <c r="R77" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="78" spans="8:18" ht="15.75" customHeight="1">
       <c r="H78" s="43"/>
       <c r="M78" s="24"/>
       <c r="R78" s="18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="79" spans="8:18" ht="15.75" customHeight="1">
       <c r="H79" s="43"/>
       <c r="M79" s="24"/>
       <c r="R79" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="80" spans="8:18" ht="15.75" customHeight="1">
       <c r="H80" s="45"/>
       <c r="M80" s="24"/>
       <c r="R80" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="81" spans="8:18" ht="15.75" customHeight="1">
       <c r="H81" s="43"/>
       <c r="M81" s="24"/>
       <c r="R81" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="82" spans="8:18" ht="15.75" customHeight="1">
       <c r="H82" s="43"/>
       <c r="M82" s="24"/>
       <c r="R82" s="18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="83" spans="8:18" ht="15.75" customHeight="1">
       <c r="H83" s="43"/>
       <c r="R83" s="18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="84" spans="8:18" ht="15.75" customHeight="1">
       <c r="H84" s="43"/>
       <c r="R84" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="85" spans="8:18" ht="15.75" customHeight="1">
       <c r="H85" s="43"/>
       <c r="R85" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="86" spans="8:18" ht="15.75" customHeight="1">
       <c r="H86" s="43"/>
       <c r="R86" s="18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="87" spans="8:18" ht="15.75" customHeight="1">
       <c r="H87" s="46"/>
       <c r="R87" s="18" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="88" spans="8:18" ht="15.75" customHeight="1">
       <c r="H88" s="46"/>
       <c r="R88" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="89" spans="8:18" ht="15.75" customHeight="1">
       <c r="H89" s="43"/>
       <c r="R89" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="90" spans="8:18" ht="15.75" customHeight="1">
       <c r="H90" s="43"/>
       <c r="R90" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="91" spans="8:18" ht="15.75" customHeight="1">
       <c r="H91" s="43"/>
       <c r="R91" s="18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="92" spans="8:18" ht="15.75" customHeight="1">
       <c r="H92" s="43"/>
       <c r="R92" s="18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="93" spans="8:18" ht="15.75" customHeight="1">
       <c r="H93" s="43"/>
       <c r="R93" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="94" spans="8:18" ht="15.75" customHeight="1">
       <c r="H94" s="43"/>
       <c r="R94" s="18" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="95" spans="8:18" ht="15.75" customHeight="1">
       <c r="H95" s="43"/>
       <c r="R95" s="18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="96" spans="8:18" ht="15.75" customHeight="1">
       <c r="H96" s="43"/>
       <c r="R96" s="18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="97" spans="8:18" ht="15.75" customHeight="1">
       <c r="H97" s="43"/>
       <c r="R97" s="18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="98" spans="8:18" ht="15.75" customHeight="1">
@@ -4710,7 +5027,7 @@
       <c r="H101" s="43"/>
       <c r="M101" s="23"/>
       <c r="R101" s="18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="102" spans="8:18" ht="15.75" customHeight="1">
@@ -4724,7 +5041,7 @@
       <c r="H103" s="43"/>
       <c r="M103" s="24"/>
       <c r="R103" s="18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="104" spans="8:18" ht="15.75" customHeight="1">
@@ -4745,7 +5062,7 @@
       <c r="H106" s="43"/>
       <c r="M106" s="39"/>
       <c r="R106" s="18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107" spans="8:18" ht="15.75" customHeight="1">
@@ -4759,7 +5076,7 @@
       <c r="H108" s="43"/>
       <c r="M108" s="39"/>
       <c r="R108" s="18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="109" spans="8:18" ht="15.75" customHeight="1">
@@ -4771,13 +5088,13 @@
     <row r="110" spans="8:18" ht="15.75" customHeight="1">
       <c r="M110" s="24"/>
       <c r="R110" s="18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="111" spans="8:18" ht="15.75" customHeight="1">
       <c r="M111" s="24"/>
       <c r="R111" s="18" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="112" spans="8:18" ht="15.75" customHeight="1">
@@ -4789,43 +5106,43 @@
     <row r="113" spans="10:18" ht="15.75" customHeight="1">
       <c r="M113" s="39"/>
       <c r="R113" s="18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="114" spans="10:18" ht="15.75" customHeight="1">
       <c r="M114" s="39"/>
       <c r="R114" s="18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="115" spans="10:18" ht="15.75" customHeight="1">
       <c r="M115" s="39"/>
       <c r="R115" s="18" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="116" spans="10:18" ht="15.75" customHeight="1">
       <c r="M116" s="24"/>
       <c r="R116" s="18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="117" spans="10:18" ht="15.75" customHeight="1">
       <c r="M117" s="24"/>
       <c r="R117" s="18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="118" spans="10:18" ht="15.75" customHeight="1">
       <c r="M118" s="39"/>
       <c r="R118" s="18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="119" spans="10:18" ht="15.75" customHeight="1">
       <c r="M119" s="39"/>
       <c r="R119" s="18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="120" spans="10:18" ht="15.75" customHeight="1">
@@ -4839,49 +5156,49 @@
       <c r="J121" s="43"/>
       <c r="M121" s="24"/>
       <c r="R121" s="18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="122" spans="10:18" ht="15.75" customHeight="1">
       <c r="J122" s="43"/>
       <c r="M122" s="24"/>
       <c r="R122" s="18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="123" spans="10:18" ht="15.75" customHeight="1">
       <c r="J123" s="43"/>
       <c r="M123" s="24"/>
       <c r="R123" s="18" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="124" spans="10:18" ht="15.75" customHeight="1">
       <c r="J124" s="43"/>
       <c r="M124" s="24"/>
       <c r="R124" s="18" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="125" spans="10:18" ht="15.75" customHeight="1">
       <c r="J125" s="43"/>
       <c r="M125" s="24"/>
       <c r="R125" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="126" spans="10:18" ht="15.75" customHeight="1">
       <c r="J126" s="43"/>
       <c r="M126" s="24"/>
       <c r="R126" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="127" spans="10:18" ht="15.75" customHeight="1">
       <c r="J127" s="43"/>
       <c r="M127" s="39"/>
       <c r="R127" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="128" spans="10:18" ht="15.75" customHeight="1">
@@ -5894,37 +6211,8 @@
   <mergeCells count="1">
     <mergeCell ref="B1:C1"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="B18:C18 C19:D19 F37:G38">
-      <formula1>$P$3:$P$130</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1">
-          <x14:formula1>
-            <xm:f>ПОНЕДЕЛЬНИК!$O$3:$O$130</xm:f>
-          </x14:formula1>
-          <xm:sqref>F3:G4 E14 B26:D28 G28 F31:G32 F34:G34 B29:B35 D29:D35 F35 D36:G36 C38 F40:G41 D42:G42</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1">
-          <x14:formula1>
-            <xm:f>СУББОТА!$O$3:$O$130</xm:f>
-          </x14:formula1>
-          <xm:sqref>B3:E4 B5:G13 B14:D14 F14:G14 B15:G17 D18:G18 B19 E19:G19 B20:G25 E26:G27 E28:F28 E29:G30 E31:E32 E33:G33 C29:C35 E34:E35 G35 B36:C36 B37:D37 B38 D38 B39:G39 B40:D40 B41:E41 B42:C42</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1">
-          <x14:formula1>
-            <xm:f>ПЯТНИЦА!$O$3:$O$130</xm:f>
-          </x14:formula1>
-          <xm:sqref>E37:E38 E40</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5933,153 +6221,196 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AI1000"/>
+  <dimension ref="A1:AI999"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="39.140625" customWidth="1"/>
-    <col min="3" max="3" width="39.28515625" customWidth="1"/>
-    <col min="4" max="4" width="38.140625" customWidth="1"/>
-    <col min="5" max="5" width="36.28515625" customWidth="1"/>
-    <col min="6" max="6" width="24.42578125" customWidth="1"/>
-    <col min="7" max="10" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
+    <col min="3" max="3" width="31.42578125" customWidth="1"/>
+    <col min="4" max="4" width="29.5703125" customWidth="1"/>
+    <col min="5" max="5" width="30.28515625" customWidth="1"/>
+    <col min="6" max="6" width="27.28515625" customWidth="1"/>
+    <col min="7" max="7" width="24.5703125" customWidth="1"/>
+    <col min="8" max="10" width="8.7109375" customWidth="1"/>
     <col min="11" max="11" width="27" customWidth="1"/>
     <col min="12" max="14" width="8.7109375" customWidth="1"/>
     <col min="15" max="15" width="26" customWidth="1"/>
     <col min="16" max="35" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="37.5" customHeight="1">
+    <row r="1" spans="1:35" ht="37.5" customHeight="1" thickBot="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="58"/>
+      <c r="C1" s="76"/>
       <c r="D1" s="7">
         <v>46267</v>
       </c>
       <c r="E1" s="9"/>
       <c r="F1" s="12"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-    </row>
-    <row r="2" spans="1:35" ht="39">
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+    </row>
+    <row r="2" spans="1:35" ht="20.25" thickBot="1">
       <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="C2" s="71" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:35" ht="26.25" customHeight="1">
+      <c r="G2" s="71" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" ht="24.95" customHeight="1" thickBot="1">
       <c r="A3" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="21"/>
+        <v>12</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" s="61" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="62"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
       <c r="O3" s="18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="26.25" customHeight="1">
+    <row r="4" spans="1:35" ht="24.95" customHeight="1" thickBot="1">
       <c r="A4" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="21"/>
+      <c r="B4" s="60" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="61" t="s">
+        <v>212</v>
+      </c>
+      <c r="D4" s="61" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="62"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
       <c r="O4" s="18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="26.25" customHeight="1">
+    <row r="5" spans="1:35" ht="24.95" customHeight="1" thickBot="1">
       <c r="A5" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="22"/>
+      <c r="B5" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
       <c r="O5" s="18" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="26.25" customHeight="1">
+    <row r="6" spans="1:35" ht="24.95" customHeight="1" thickBot="1">
       <c r="A6" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="22"/>
+      <c r="B6" s="60" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="61" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
       <c r="O6" s="18" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="26.25" customHeight="1">
+    <row r="7" spans="1:35" ht="24.95" customHeight="1" thickBot="1">
       <c r="A7" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="22"/>
+      <c r="B7" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="61" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
       <c r="O7" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="26.25" customHeight="1">
+    <row r="8" spans="1:35" ht="24.95" customHeight="1" thickBot="1">
       <c r="A8" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="22"/>
+      <c r="B8" s="60" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
       <c r="O8" s="18" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="26.25" customHeight="1">
+    <row r="9" spans="1:35" ht="24.95" customHeight="1" thickBot="1">
       <c r="A9" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="22"/>
+      <c r="B9" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="61" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="J9" s="25"/>
@@ -6111,494 +6442,688 @@
       <c r="AH9" s="25"/>
       <c r="AI9" s="25"/>
     </row>
-    <row r="10" spans="1:35" ht="26.25" customHeight="1">
+    <row r="10" spans="1:35" ht="24.95" customHeight="1" thickBot="1">
       <c r="A10" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="30"/>
+      <c r="B10" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="61" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
       <c r="K10" s="24"/>
       <c r="O10" s="18" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="26.25" customHeight="1">
+    <row r="11" spans="1:35" ht="24.95" customHeight="1" thickBot="1">
       <c r="A11" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="22"/>
+        <v>48</v>
+      </c>
+      <c r="B11" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
       <c r="K11" s="24"/>
       <c r="O11" s="18" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="26.25" customHeight="1">
+    <row r="12" spans="1:35" ht="24.95" customHeight="1" thickBot="1">
       <c r="A12" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="22"/>
+        <v>52</v>
+      </c>
+      <c r="B12" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="61" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="62"/>
       <c r="K12" s="28"/>
       <c r="O12" s="18" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="28.5" customHeight="1">
+    <row r="13" spans="1:35" ht="24.95" customHeight="1" thickBot="1">
       <c r="A13" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="22"/>
+        <v>54</v>
+      </c>
+      <c r="B13" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="61" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" s="61" t="s">
+        <v>244</v>
+      </c>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
       <c r="K13" s="28"/>
       <c r="O13" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:35" ht="26.25" customHeight="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" ht="24.95" customHeight="1" thickBot="1">
       <c r="A14" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="22"/>
+      <c r="B14" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="61" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="61" t="s">
+        <v>171</v>
+      </c>
+      <c r="E14" s="64"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
       <c r="K14" s="28"/>
       <c r="O14" s="18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:35" ht="27.75" customHeight="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" ht="24.95" customHeight="1" thickBot="1">
       <c r="A15" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="22"/>
+      <c r="B15" s="60" t="s">
+        <v>178</v>
+      </c>
+      <c r="C15" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="65" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
       <c r="K15" s="31"/>
       <c r="O15" s="18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:35" ht="28.5" customHeight="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" ht="24.95" customHeight="1" thickBot="1">
       <c r="A16" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="15"/>
+      <c r="B16" s="60" t="s">
+        <v>233</v>
+      </c>
+      <c r="C16" s="61" t="s">
+        <v>178</v>
+      </c>
+      <c r="D16" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="62"/>
+      <c r="F16" s="64"/>
+      <c r="G16" s="64"/>
       <c r="K16" s="31"/>
       <c r="O16" s="18" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="27" customHeight="1">
+    <row r="17" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A17" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="61" t="s">
+        <v>234</v>
+      </c>
+      <c r="E17" s="61" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="G17" s="64"/>
       <c r="K17" s="31"/>
       <c r="O17" s="18" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="28.5" customHeight="1">
+    <row r="18" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A18" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="F18" s="65" t="s">
+        <v>235</v>
+      </c>
+      <c r="G18" s="61" t="s">
+        <v>47</v>
+      </c>
       <c r="K18" s="28"/>
       <c r="O18" s="18" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="26.25" customHeight="1">
+    <row r="19" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A19" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="61" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="61" t="s">
+        <v>236</v>
+      </c>
+      <c r="G19" s="65" t="s">
+        <v>235</v>
+      </c>
       <c r="K19" s="28"/>
       <c r="O19" s="18" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="26.25" customHeight="1">
+    <row r="20" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A20" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
+      <c r="B20" s="67"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="61" t="s">
+        <v>116</v>
+      </c>
       <c r="K20" s="31"/>
       <c r="O20" s="18" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="26.25" customHeight="1">
+    <row r="21" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A21" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="61" t="s">
+        <v>237</v>
+      </c>
+      <c r="F21" s="61" t="s">
+        <v>238</v>
+      </c>
+      <c r="G21" s="65" t="s">
+        <v>75</v>
+      </c>
       <c r="K21" s="31"/>
       <c r="O21" s="18" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="27.75" customHeight="1">
+    <row r="22" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A22" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="61" t="s">
+        <v>238</v>
+      </c>
       <c r="K22" s="28"/>
       <c r="O22" s="18" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="25.5" customHeight="1">
+    <row r="23" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A23" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" s="65" t="s">
+        <v>239</v>
+      </c>
+      <c r="G23" s="64"/>
       <c r="K23" s="31"/>
       <c r="O23" s="18" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="26.25" customHeight="1">
+    <row r="24" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A24" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="G24" s="65" t="s">
+        <v>239</v>
+      </c>
       <c r="K24" s="28"/>
       <c r="O24" s="18" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="26.25" customHeight="1">
+    <row r="25" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A25" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="65" t="s">
+        <v>212</v>
+      </c>
+      <c r="G25" s="64"/>
       <c r="K25" s="28"/>
       <c r="O25" s="18" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="26.25" customHeight="1">
+    <row r="26" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A26" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="61" t="s">
+        <v>50</v>
+      </c>
+      <c r="F26" s="65" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="65" t="s">
+        <v>212</v>
+      </c>
       <c r="K26" s="31"/>
       <c r="O26" s="18" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="26.25" customHeight="1">
+    <row r="27" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A27" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="65" t="s">
+        <v>95</v>
+      </c>
+      <c r="G27" s="65" t="s">
+        <v>240</v>
+      </c>
       <c r="K27" s="31"/>
       <c r="O27" s="18" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="26.25" customHeight="1">
+    <row r="28" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A28" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="15"/>
+      <c r="B28" s="66"/>
+      <c r="C28" s="64"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" s="61" t="s">
+        <v>97</v>
+      </c>
+      <c r="G28" s="65" t="s">
+        <v>168</v>
+      </c>
       <c r="K28" s="31"/>
       <c r="O28" s="18" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="26.25" customHeight="1">
+    <row r="29" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A29" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="64"/>
+      <c r="D29" s="64"/>
+      <c r="E29" s="61" t="s">
+        <v>235</v>
+      </c>
+      <c r="F29" s="61" t="s">
+        <v>133</v>
+      </c>
+      <c r="G29" s="61" t="s">
+        <v>100</v>
+      </c>
       <c r="K29" s="28"/>
       <c r="O29" s="18" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="26.25" customHeight="1">
+    <row r="30" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A30" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="22"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="64"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="F30" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="G30" s="61" t="s">
+        <v>133</v>
+      </c>
       <c r="K30" s="31"/>
       <c r="O30" s="18" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="26.25" customHeight="1">
+    <row r="31" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A31" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="64"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="61" t="s">
+        <v>245</v>
+      </c>
+      <c r="F31" s="65" t="s">
+        <v>241</v>
+      </c>
+      <c r="G31" s="65" t="s">
+        <v>246</v>
+      </c>
       <c r="K31" s="28"/>
       <c r="O31" s="18" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="26.25" customHeight="1">
+    <row r="32" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A32" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="B32" s="22"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
+      <c r="B32" s="67"/>
+      <c r="C32" s="64"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="61" t="s">
+        <v>125</v>
+      </c>
+      <c r="F32" s="61" t="s">
+        <v>245</v>
+      </c>
+      <c r="G32" s="65" t="s">
+        <v>241</v>
+      </c>
       <c r="K32" s="28"/>
       <c r="O32" s="18" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="26.25" customHeight="1">
+    <row r="33" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A33" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B33" s="22"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
+      <c r="B33" s="67"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="F33" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="G33" s="65" t="s">
+        <v>245</v>
+      </c>
       <c r="K33" s="31"/>
       <c r="O33" s="18" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="26.25" customHeight="1">
+    <row r="34" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A34" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="B34" s="22"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="64"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="61" t="s">
+        <v>140</v>
+      </c>
+      <c r="F34" s="61" t="s">
+        <v>140</v>
+      </c>
+      <c r="G34" s="61" t="s">
+        <v>140</v>
+      </c>
       <c r="K34" s="24"/>
       <c r="O34" s="18" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="26.25" customHeight="1">
+    <row r="35" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A35" s="36" t="s">
-        <v>122</v>
-      </c>
-      <c r="B35" s="22"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="15"/>
+        <v>121</v>
+      </c>
+      <c r="B35" s="67"/>
+      <c r="C35" s="64"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="F35" s="61" t="s">
+        <v>106</v>
+      </c>
+      <c r="G35" s="61" t="s">
+        <v>106</v>
+      </c>
       <c r="K35" s="24"/>
       <c r="O35" s="18" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="25.5" customHeight="1">
+    <row r="36" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A36" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="41"/>
+        <v>130</v>
+      </c>
+      <c r="B36" s="60" t="s">
+        <v>133</v>
+      </c>
+      <c r="C36" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="62"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="68"/>
       <c r="K36" s="24"/>
       <c r="O36" s="18" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="15.75" customHeight="1">
+    <row r="37" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A37" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="B37" s="16"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
+        <v>137</v>
+      </c>
+      <c r="B37" s="60" t="s">
+        <v>247</v>
+      </c>
+      <c r="C37" s="61" t="s">
+        <v>133</v>
+      </c>
+      <c r="D37" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="E37" s="62"/>
+      <c r="F37" s="64"/>
+      <c r="G37" s="64"/>
       <c r="K37" s="37"/>
       <c r="O37" s="18" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="15.75" customHeight="1">
+    <row r="38" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A38" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
+        <v>147</v>
+      </c>
+      <c r="B38" s="72" t="s">
+        <v>134</v>
+      </c>
+      <c r="C38" s="65" t="s">
+        <v>243</v>
+      </c>
+      <c r="D38" s="61" t="s">
+        <v>133</v>
+      </c>
+      <c r="E38" s="62"/>
+      <c r="F38" s="64"/>
+      <c r="G38" s="64"/>
       <c r="K38" s="31"/>
       <c r="O38" s="18" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="15.75" customHeight="1">
+    <row r="39" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A39" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="B39" s="16"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
+        <v>157</v>
+      </c>
+      <c r="B39" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39" s="61" t="s">
+        <v>136</v>
+      </c>
+      <c r="D39" s="65" t="s">
+        <v>245</v>
+      </c>
+      <c r="E39" s="64"/>
+      <c r="F39" s="64"/>
+      <c r="G39" s="64"/>
       <c r="K39" s="31"/>
       <c r="O39" s="18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="15.75" customHeight="1">
+    <row r="40" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A40" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
+        <v>169</v>
+      </c>
+      <c r="B40" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" s="65" t="s">
+        <v>245</v>
+      </c>
+      <c r="D40" s="61" t="s">
+        <v>136</v>
+      </c>
+      <c r="E40" s="62"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="64"/>
       <c r="K40" s="31"/>
       <c r="O40" s="18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="15.75" customHeight="1">
+    <row r="41" spans="1:15" ht="24.95" customHeight="1" thickBot="1">
       <c r="A41" s="36" t="s">
-        <v>177</v>
-      </c>
-      <c r="B41" s="16"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="35"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
+        <v>176</v>
+      </c>
+      <c r="B41" s="60" t="s">
+        <v>154</v>
+      </c>
+      <c r="C41" s="61" t="s">
+        <v>154</v>
+      </c>
+      <c r="D41" s="61" t="s">
+        <v>154</v>
+      </c>
+      <c r="E41" s="64"/>
+      <c r="F41" s="69"/>
+      <c r="G41" s="69"/>
       <c r="K41" s="31"/>
       <c r="O41" s="18" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="15.75" customHeight="1">
+      <c r="B42" s="55"/>
+      <c r="C42" s="55"/>
+      <c r="D42" s="55"/>
+      <c r="E42" s="55"/>
+      <c r="F42" s="55"/>
+      <c r="G42" s="55"/>
       <c r="K42" s="28"/>
       <c r="O42" s="18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="15.75" customHeight="1">
-      <c r="K43" s="28"/>
+      <c r="K43" s="31"/>
       <c r="O43" s="18" t="s">
         <v>119</v>
       </c>
@@ -6610,15 +7135,15 @@
       </c>
     </row>
     <row r="45" spans="1:15" ht="15.75" customHeight="1">
-      <c r="K45" s="31"/>
+      <c r="K45" s="38"/>
       <c r="O45" s="18" t="s">
-        <v>121</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="15.75" customHeight="1">
-      <c r="K46" s="38"/>
+      <c r="K46" s="24"/>
       <c r="O46" s="18" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="15.75" customHeight="1">
@@ -6628,7 +7153,7 @@
       </c>
     </row>
     <row r="48" spans="1:15" ht="15.75" customHeight="1">
-      <c r="K48" s="24"/>
+      <c r="K48" s="39"/>
       <c r="O48" s="18" t="s">
         <v>124</v>
       </c>
@@ -6636,25 +7161,25 @@
     <row r="49" spans="11:15" ht="15.75" customHeight="1">
       <c r="K49" s="39"/>
       <c r="O49" s="18" t="s">
-        <v>125</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="11:15" ht="15.75" customHeight="1">
       <c r="K50" s="39"/>
       <c r="O50" s="18" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="11:15" ht="15.75" customHeight="1">
-      <c r="K51" s="39"/>
+      <c r="K51" s="24"/>
       <c r="O51" s="18" t="s">
-        <v>50</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="11:15" ht="15.75" customHeight="1">
       <c r="K52" s="24"/>
       <c r="O52" s="18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53" spans="11:15" ht="15.75" customHeight="1">
@@ -6664,7 +7189,7 @@
       </c>
     </row>
     <row r="54" spans="11:15" ht="15.75" customHeight="1">
-      <c r="K54" s="24"/>
+      <c r="K54" s="39"/>
       <c r="O54" s="18" t="s">
         <v>129</v>
       </c>
@@ -6672,11 +7197,11 @@
     <row r="55" spans="11:15" ht="15.75" customHeight="1">
       <c r="K55" s="39"/>
       <c r="O55" s="18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="11:15" ht="15.75" customHeight="1">
-      <c r="K56" s="39"/>
+      <c r="K56" s="24"/>
       <c r="O56" s="18" t="s">
         <v>132</v>
       </c>
@@ -6684,25 +7209,25 @@
     <row r="57" spans="11:15" ht="15.75" customHeight="1">
       <c r="K57" s="24"/>
       <c r="O57" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58" spans="11:15" ht="15.75" customHeight="1">
       <c r="K58" s="24"/>
       <c r="O58" s="18" t="s">
-        <v>135</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="11:15" ht="15.75" customHeight="1">
       <c r="K59" s="24"/>
       <c r="O59" s="18" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60" spans="11:15" ht="15.75" customHeight="1">
       <c r="K60" s="24"/>
       <c r="O60" s="18" t="s">
-        <v>97</v>
+        <v>135</v>
       </c>
     </row>
     <row r="61" spans="11:15" ht="15.75" customHeight="1">
@@ -6714,7 +7239,7 @@
     <row r="62" spans="11:15" ht="15.75" customHeight="1">
       <c r="K62" s="24"/>
       <c r="O62" s="18" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63" spans="11:15" ht="15.75" customHeight="1">
@@ -6768,7 +7293,7 @@
     <row r="71" spans="11:15" ht="15.75" customHeight="1">
       <c r="K71" s="24"/>
       <c r="O71" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="72" spans="11:15" ht="15.75" customHeight="1">
@@ -6822,7 +7347,7 @@
     <row r="80" spans="11:15" ht="15.75" customHeight="1">
       <c r="K80" s="24"/>
       <c r="O80" s="18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="81" spans="11:15" ht="15.75" customHeight="1">
@@ -6832,7 +7357,6 @@
       </c>
     </row>
     <row r="82" spans="11:15" ht="15.75" customHeight="1">
-      <c r="K82" s="24"/>
       <c r="O82" s="18" t="s">
         <v>160</v>
       </c>
@@ -6879,17 +7403,17 @@
     </row>
     <row r="91" spans="11:15" ht="15.75" customHeight="1">
       <c r="O91" s="18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="92" spans="11:15" ht="15.75" customHeight="1">
       <c r="O92" s="18" t="s">
-        <v>171</v>
+        <v>49</v>
       </c>
     </row>
     <row r="93" spans="11:15" ht="15.75" customHeight="1">
       <c r="O93" s="18" t="s">
-        <v>48</v>
+        <v>171</v>
       </c>
     </row>
     <row r="94" spans="11:15" ht="15.75" customHeight="1">
@@ -6909,76 +7433,77 @@
     </row>
     <row r="97" spans="11:15" ht="15.75" customHeight="1">
       <c r="O97" s="18" t="s">
-        <v>175</v>
+        <v>42</v>
       </c>
     </row>
     <row r="98" spans="11:15" ht="15.75" customHeight="1">
       <c r="O98" s="18" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
     </row>
     <row r="99" spans="11:15" ht="15.75" customHeight="1">
       <c r="O99" s="18" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
     </row>
     <row r="100" spans="11:15" ht="15.75" customHeight="1">
+      <c r="K100" s="23"/>
       <c r="O100" s="18" t="s">
-        <v>80</v>
+        <v>175</v>
       </c>
     </row>
     <row r="101" spans="11:15" ht="15.75" customHeight="1">
-      <c r="K101" s="23"/>
+      <c r="K101" s="24"/>
       <c r="O101" s="18" t="s">
-        <v>176</v>
+        <v>95</v>
       </c>
     </row>
     <row r="102" spans="11:15" ht="15.75" customHeight="1">
       <c r="K102" s="24"/>
       <c r="O102" s="18" t="s">
-        <v>95</v>
+        <v>177</v>
       </c>
     </row>
     <row r="103" spans="11:15" ht="15.75" customHeight="1">
       <c r="K103" s="24"/>
       <c r="O103" s="18" t="s">
-        <v>178</v>
+        <v>37</v>
       </c>
     </row>
     <row r="104" spans="11:15" ht="15.75" customHeight="1">
       <c r="K104" s="24"/>
       <c r="O104" s="18" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="105" spans="11:15" ht="15.75" customHeight="1">
-      <c r="K105" s="24"/>
+      <c r="K105" s="39"/>
       <c r="O105" s="18" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="106" spans="11:15" ht="15.75" customHeight="1">
       <c r="K106" s="39"/>
       <c r="O106" s="18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="107" spans="11:15" ht="15.75" customHeight="1">
       <c r="K107" s="39"/>
       <c r="O107" s="18" t="s">
-        <v>15</v>
+        <v>178</v>
       </c>
     </row>
     <row r="108" spans="11:15" ht="15.75" customHeight="1">
-      <c r="K108" s="39"/>
+      <c r="K108" s="24"/>
       <c r="O108" s="18" t="s">
-        <v>179</v>
+        <v>36</v>
       </c>
     </row>
     <row r="109" spans="11:15" ht="15.75" customHeight="1">
       <c r="K109" s="24"/>
       <c r="O109" s="18" t="s">
-        <v>36</v>
+        <v>179</v>
       </c>
     </row>
     <row r="110" spans="11:15" ht="15.75" customHeight="1">
@@ -6990,13 +7515,13 @@
     <row r="111" spans="11:15" ht="15.75" customHeight="1">
       <c r="K111" s="24"/>
       <c r="O111" s="18" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="112" spans="11:15" ht="15.75" customHeight="1">
+      <c r="K112" s="39"/>
+      <c r="O112" s="18" t="s">
         <v>181</v>
-      </c>
-    </row>
-    <row r="112" spans="11:15" ht="15.75" customHeight="1">
-      <c r="K112" s="24"/>
-      <c r="O112" s="18" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="113" spans="11:15" ht="15.75" customHeight="1">
@@ -7012,7 +7537,7 @@
       </c>
     </row>
     <row r="115" spans="11:15" ht="15.75" customHeight="1">
-      <c r="K115" s="39"/>
+      <c r="K115" s="24"/>
       <c r="O115" s="18" t="s">
         <v>184</v>
       </c>
@@ -7024,7 +7549,7 @@
       </c>
     </row>
     <row r="117" spans="11:15" ht="15.75" customHeight="1">
-      <c r="K117" s="24"/>
+      <c r="K117" s="39"/>
       <c r="O117" s="18" t="s">
         <v>186</v>
       </c>
@@ -7036,15 +7561,15 @@
       </c>
     </row>
     <row r="119" spans="11:15" ht="15.75" customHeight="1">
-      <c r="K119" s="39"/>
+      <c r="K119" s="24"/>
       <c r="O119" s="18" t="s">
-        <v>188</v>
+        <v>60</v>
       </c>
     </row>
     <row r="120" spans="11:15" ht="15.75" customHeight="1">
       <c r="K120" s="24"/>
       <c r="O120" s="18" t="s">
-        <v>60</v>
+        <v>188</v>
       </c>
     </row>
     <row r="121" spans="11:15" ht="15.75" customHeight="1">
@@ -7078,19 +7603,16 @@
       </c>
     </row>
     <row r="126" spans="11:15" ht="15.75" customHeight="1">
-      <c r="K126" s="24"/>
+      <c r="K126" s="39"/>
       <c r="O126" s="18" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="127" spans="11:15" ht="15.75" customHeight="1">
       <c r="K127" s="39"/>
-      <c r="O127" s="18" t="s">
-        <v>195</v>
-      </c>
     </row>
     <row r="128" spans="11:15" ht="15.75" customHeight="1">
-      <c r="K128" s="39"/>
+      <c r="K128" s="24"/>
     </row>
     <row r="129" spans="11:11" ht="15.75" customHeight="1">
       <c r="K129" s="24"/>
@@ -7102,10 +7624,10 @@
       <c r="K131" s="24"/>
     </row>
     <row r="132" spans="11:11" ht="15.75" customHeight="1">
-      <c r="K132" s="24"/>
+      <c r="K132" s="39"/>
     </row>
     <row r="133" spans="11:11" ht="15.75" customHeight="1">
-      <c r="K133" s="39"/>
+      <c r="K133" s="24"/>
     </row>
     <row r="134" spans="11:11" ht="15.75" customHeight="1">
       <c r="K134" s="24"/>
@@ -7129,10 +7651,10 @@
       <c r="K140" s="24"/>
     </row>
     <row r="141" spans="11:11" ht="15.75" customHeight="1">
-      <c r="K141" s="24"/>
+      <c r="K141" s="39"/>
     </row>
     <row r="142" spans="11:11" ht="15.75" customHeight="1">
-      <c r="K142" s="39"/>
+      <c r="K142" s="24"/>
     </row>
     <row r="143" spans="11:11" ht="15.75" customHeight="1">
       <c r="K143" s="24"/>
@@ -7141,13 +7663,13 @@
       <c r="K144" s="24"/>
     </row>
     <row r="145" spans="11:11" ht="15.75" customHeight="1">
-      <c r="K145" s="24"/>
+      <c r="K145" s="39"/>
     </row>
     <row r="146" spans="11:11" ht="15.75" customHeight="1">
       <c r="K146" s="39"/>
     </row>
     <row r="147" spans="11:11" ht="15.75" customHeight="1">
-      <c r="K147" s="39"/>
+      <c r="K147" s="24"/>
     </row>
     <row r="148" spans="11:11" ht="15.75" customHeight="1">
       <c r="K148" s="24"/>
@@ -7168,18 +7690,18 @@
       <c r="K153" s="24"/>
     </row>
     <row r="154" spans="11:11" ht="15.75" customHeight="1">
-      <c r="K154" s="24"/>
+      <c r="K154" s="39"/>
     </row>
     <row r="155" spans="11:11" ht="15.75" customHeight="1">
       <c r="K155" s="39"/>
     </row>
-    <row r="156" spans="11:11" ht="15.75" customHeight="1">
-      <c r="K156" s="39"/>
-    </row>
+    <row r="156" spans="11:11" ht="15.75" customHeight="1"/>
     <row r="157" spans="11:11" ht="15.75" customHeight="1"/>
-    <row r="158" spans="11:11" ht="15.75" customHeight="1"/>
+    <row r="158" spans="11:11" ht="15.75" customHeight="1">
+      <c r="K158" s="23"/>
+    </row>
     <row r="159" spans="11:11" ht="15.75" customHeight="1">
-      <c r="K159" s="23"/>
+      <c r="K159" s="24"/>
     </row>
     <row r="160" spans="11:11" ht="15.75" customHeight="1">
       <c r="K160" s="24"/>
@@ -7257,11 +7779,9 @@
       <c r="K184" s="24"/>
     </row>
     <row r="185" spans="11:11" ht="15.75" customHeight="1">
-      <c r="K185" s="24"/>
-    </row>
-    <row r="186" spans="11:11" ht="15.75" customHeight="1">
-      <c r="K186" s="44"/>
-    </row>
+      <c r="K185" s="44"/>
+    </row>
+    <row r="186" spans="11:11" ht="15.75" customHeight="1"/>
     <row r="187" spans="11:11" ht="15.75" customHeight="1"/>
     <row r="188" spans="11:11" ht="15.75" customHeight="1"/>
     <row r="189" spans="11:11" ht="15.75" customHeight="1"/>
@@ -8075,40 +8595,13 @@
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="G1:H1"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="F3:G4 E14 B26:D28 G28 F31:G32 F34:G34 B29:B35 D29:D35 F35 D36:G36 C38 F40:G41">
-      <formula1>$O$3:$O$130</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B18:C18 C19:D19 F37:G38">
-      <formula1>$P$3:$P$130</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.11811023622047244" right="0.13629737609329445" top="0.7" bottom="0.7" header="0" footer="0"/>
   <pageSetup fitToHeight="0" orientation="portrait"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1">
-          <x14:formula1>
-            <xm:f>СУББОТА!$O$3:$O$130</xm:f>
-          </x14:formula1>
-          <xm:sqref>B3:E4 B5:G13 B14:D14 F14:G14 B15:G17 D18:G18 B19 E19:G19 B20:G25 E26:G27 E28:F28 E29:G30 E31:E32 E33:G33 C29:C35 E34:E35 G35 B36:C36 B37:D37 B38 D38 B39:G39 B40:D40 B41:E41</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1">
-          <x14:formula1>
-            <xm:f>ПЯТНИЦА!$O$3:$O$130</xm:f>
-          </x14:formula1>
-          <xm:sqref>E37:E38 E40</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -8136,10 +8629,10 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="58"/>
+      <c r="C1" s="76"/>
       <c r="D1" s="2">
         <v>46268</v>
       </c>
@@ -8166,12 +8659,12 @@
         <v>9</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="26.25" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -8286,7 +8779,7 @@
     </row>
     <row r="11" spans="1:15" ht="28.5" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
@@ -8301,7 +8794,7 @@
     </row>
     <row r="12" spans="1:15" ht="28.5" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -8316,7 +8809,7 @@
     </row>
     <row r="13" spans="1:15" ht="26.25" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -8326,7 +8819,7 @@
       <c r="G13" s="22"/>
       <c r="L13" s="28"/>
       <c r="O13" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="26.25" customHeight="1">
@@ -8341,7 +8834,7 @@
       <c r="G14" s="22"/>
       <c r="L14" s="31"/>
       <c r="O14" s="18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="26.25" customHeight="1">
@@ -8356,7 +8849,7 @@
       <c r="G15" s="22"/>
       <c r="L15" s="31"/>
       <c r="O15" s="18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="26.25" customHeight="1">
@@ -8649,7 +9142,7 @@
     </row>
     <row r="35" spans="1:15" ht="26.25" customHeight="1">
       <c r="A35" s="36" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B35" s="22"/>
       <c r="C35" s="15"/>
@@ -8664,7 +9157,7 @@
     </row>
     <row r="36" spans="1:15" ht="26.25" customHeight="1">
       <c r="A36" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="15"/>
@@ -8679,7 +9172,7 @@
     </row>
     <row r="37" spans="1:15" ht="15.75" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="15"/>
@@ -8694,7 +9187,7 @@
     </row>
     <row r="38" spans="1:15" ht="15.75" customHeight="1">
       <c r="A38" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="15"/>
@@ -8709,7 +9202,7 @@
     </row>
     <row r="39" spans="1:15" ht="15.75" customHeight="1">
       <c r="A39" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="15"/>
@@ -8724,7 +9217,7 @@
     </row>
     <row r="40" spans="1:15" ht="15.75" customHeight="1">
       <c r="A40" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B40" s="16"/>
       <c r="C40" s="15"/>
@@ -8739,7 +9232,7 @@
     </row>
     <row r="41" spans="1:15" ht="15.75" customHeight="1">
       <c r="A41" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B41" s="16"/>
       <c r="C41" s="15"/>
@@ -8761,19 +9254,19 @@
     <row r="43" spans="1:15" ht="15.75" customHeight="1">
       <c r="L43" s="28"/>
       <c r="O43" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="15.75" customHeight="1">
       <c r="L44" s="31"/>
       <c r="O44" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="15.75" customHeight="1">
       <c r="L45" s="31"/>
       <c r="O45" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="15.75" customHeight="1">
@@ -8785,19 +9278,19 @@
     <row r="47" spans="1:15" ht="15.75" customHeight="1">
       <c r="L47" s="24"/>
       <c r="O47" s="18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="15.75" customHeight="1">
       <c r="L48" s="24"/>
       <c r="O48" s="18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="12:15" ht="15.75" customHeight="1">
       <c r="L49" s="39"/>
       <c r="O49" s="18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50" spans="12:15" ht="15.75" customHeight="1">
@@ -8809,49 +9302,49 @@
     <row r="51" spans="12:15" ht="15.75" customHeight="1">
       <c r="L51" s="39"/>
       <c r="O51" s="18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="12:15" ht="15.75" customHeight="1">
       <c r="L52" s="24"/>
       <c r="O52" s="18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="12:15" ht="15.75" customHeight="1">
       <c r="L53" s="24"/>
       <c r="O53" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54" spans="12:15" ht="15.75" customHeight="1">
       <c r="L54" s="24"/>
       <c r="O54" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="12:15" ht="15.75" customHeight="1">
       <c r="L55" s="39"/>
       <c r="O55" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="12:15" ht="15.75" customHeight="1">
       <c r="L56" s="39"/>
       <c r="O56" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="12:15" ht="15.75" customHeight="1">
       <c r="L57" s="24"/>
       <c r="O57" s="18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="12:15" ht="15.75" customHeight="1">
       <c r="L58" s="24"/>
       <c r="O58" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="12:15" ht="15.75" customHeight="1">
@@ -8869,208 +9362,208 @@
     <row r="61" spans="12:15" ht="15.75" customHeight="1">
       <c r="L61" s="24"/>
       <c r="O61" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="12:15" ht="15.75" customHeight="1">
       <c r="L62" s="24"/>
       <c r="O62" s="18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="12:15" ht="15.75" customHeight="1">
       <c r="L63" s="24"/>
       <c r="O63" s="18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="64" spans="12:15" ht="15.75" customHeight="1">
       <c r="L64" s="24"/>
       <c r="O64" s="18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="12:15" ht="15.75" customHeight="1">
       <c r="L65" s="24"/>
       <c r="O65" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="12:15" ht="15.75" customHeight="1">
       <c r="L66" s="24"/>
       <c r="O66" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="67" spans="12:15" ht="15.75" customHeight="1">
       <c r="L67" s="24"/>
       <c r="O67" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="68" spans="12:15" ht="15.75" customHeight="1">
       <c r="L68" s="24"/>
       <c r="O68" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69" spans="12:15" ht="15.75" customHeight="1">
       <c r="L69" s="24"/>
       <c r="O69" s="18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="12:15" ht="15.75" customHeight="1">
       <c r="L70" s="24"/>
       <c r="O70" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="71" spans="12:15" ht="15.75" customHeight="1">
       <c r="L71" s="24"/>
       <c r="O71" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="12:15" ht="15.75" customHeight="1">
       <c r="L72" s="24"/>
       <c r="O72" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73" spans="12:15" ht="15.75" customHeight="1">
       <c r="L73" s="24"/>
       <c r="O73" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="74" spans="12:15" ht="15.75" customHeight="1">
       <c r="L74" s="24"/>
       <c r="O74" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="75" spans="12:15" ht="15.75" customHeight="1">
       <c r="L75" s="24"/>
       <c r="O75" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="76" spans="12:15" ht="15.75" customHeight="1">
       <c r="L76" s="24"/>
       <c r="O76" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="77" spans="12:15" ht="15.75" customHeight="1">
       <c r="L77" s="24"/>
       <c r="O77" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="78" spans="12:15" ht="15.75" customHeight="1">
       <c r="L78" s="24"/>
       <c r="O78" s="18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="79" spans="12:15" ht="15.75" customHeight="1">
       <c r="L79" s="24"/>
       <c r="O79" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="80" spans="12:15" ht="15.75" customHeight="1">
       <c r="L80" s="24"/>
       <c r="O80" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="81" spans="12:15" ht="15.75" customHeight="1">
       <c r="L81" s="24"/>
       <c r="O81" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="82" spans="12:15" ht="15.75" customHeight="1">
       <c r="L82" s="24"/>
       <c r="O82" s="18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="83" spans="12:15" ht="15.75" customHeight="1">
       <c r="O83" s="18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="84" spans="12:15" ht="15.75" customHeight="1">
       <c r="O84" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="85" spans="12:15" ht="15.75" customHeight="1">
       <c r="O85" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="86" spans="12:15" ht="15.75" customHeight="1">
       <c r="O86" s="18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="87" spans="12:15" ht="15.75" customHeight="1">
       <c r="O87" s="18" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="88" spans="12:15" ht="15.75" customHeight="1">
       <c r="O88" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="89" spans="12:15" ht="15.75" customHeight="1">
       <c r="O89" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="90" spans="12:15" ht="15.75" customHeight="1">
       <c r="O90" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="91" spans="12:15" ht="15.75" customHeight="1">
       <c r="O91" s="18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="92" spans="12:15" ht="15.75" customHeight="1">
       <c r="O92" s="18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="93" spans="12:15" ht="15.75" customHeight="1">
       <c r="O93" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="94" spans="12:15" ht="15.75" customHeight="1">
       <c r="O94" s="18" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="95" spans="12:15" ht="15.75" customHeight="1">
       <c r="O95" s="18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="96" spans="12:15" ht="15.75" customHeight="1">
       <c r="O96" s="18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="97" spans="12:15" ht="15.75" customHeight="1">
       <c r="O97" s="18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="98" spans="12:15" ht="15.75" customHeight="1">
@@ -9091,7 +9584,7 @@
     <row r="101" spans="12:15" ht="15.75" customHeight="1">
       <c r="L101" s="23"/>
       <c r="O101" s="18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="102" spans="12:15" ht="15.75" customHeight="1">
@@ -9103,7 +9596,7 @@
     <row r="103" spans="12:15" ht="15.75" customHeight="1">
       <c r="L103" s="24"/>
       <c r="O103" s="18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="104" spans="12:15" ht="15.75" customHeight="1">
@@ -9121,7 +9614,7 @@
     <row r="106" spans="12:15" ht="15.75" customHeight="1">
       <c r="L106" s="39"/>
       <c r="O106" s="18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107" spans="12:15" ht="15.75" customHeight="1">
@@ -9133,7 +9626,7 @@
     <row r="108" spans="12:15" ht="15.75" customHeight="1">
       <c r="L108" s="39"/>
       <c r="O108" s="18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="109" spans="12:15" ht="15.75" customHeight="1">
@@ -9145,13 +9638,13 @@
     <row r="110" spans="12:15" ht="15.75" customHeight="1">
       <c r="L110" s="24"/>
       <c r="O110" s="18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="111" spans="12:15" ht="15.75" customHeight="1">
       <c r="L111" s="24"/>
       <c r="O111" s="18" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="112" spans="12:15" ht="15.75" customHeight="1">
@@ -9163,43 +9656,43 @@
     <row r="113" spans="12:15" ht="15.75" customHeight="1">
       <c r="L113" s="39"/>
       <c r="O113" s="18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="114" spans="12:15" ht="15.75" customHeight="1">
       <c r="L114" s="39"/>
       <c r="O114" s="18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="115" spans="12:15" ht="15.75" customHeight="1">
       <c r="L115" s="39"/>
       <c r="O115" s="18" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="116" spans="12:15" ht="15.75" customHeight="1">
       <c r="L116" s="24"/>
       <c r="O116" s="18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="117" spans="12:15" ht="15.75" customHeight="1">
       <c r="L117" s="24"/>
       <c r="O117" s="18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="118" spans="12:15" ht="15.75" customHeight="1">
       <c r="L118" s="39"/>
       <c r="O118" s="18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="119" spans="12:15" ht="15.75" customHeight="1">
       <c r="L119" s="39"/>
       <c r="O119" s="18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="120" spans="12:15" ht="15.75" customHeight="1">
@@ -9211,43 +9704,43 @@
     <row r="121" spans="12:15" ht="15.75" customHeight="1">
       <c r="L121" s="24"/>
       <c r="O121" s="18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="122" spans="12:15" ht="15.75" customHeight="1">
       <c r="L122" s="24"/>
       <c r="O122" s="18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="123" spans="12:15" ht="15.75" customHeight="1">
       <c r="L123" s="24"/>
       <c r="O123" s="18" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="124" spans="12:15" ht="15.75" customHeight="1">
       <c r="L124" s="24"/>
       <c r="O124" s="18" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="125" spans="12:15" ht="15.75" customHeight="1">
       <c r="L125" s="24"/>
       <c r="O125" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="126" spans="12:15" ht="15.75" customHeight="1">
       <c r="L126" s="24"/>
       <c r="O126" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="127" spans="12:15" ht="15.75" customHeight="1">
       <c r="L127" s="39"/>
       <c r="O127" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="128" spans="12:15" ht="15.75" customHeight="1">
@@ -10298,17 +10791,17 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57" t="s">
-        <v>196</v>
-      </c>
-      <c r="C1" s="58"/>
+      <c r="B1" s="75" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1" s="76"/>
       <c r="D1" s="7">
         <v>46269</v>
       </c>
       <c r="E1" s="47"/>
       <c r="F1" s="13"/>
     </row>
-    <row r="2" spans="1:15" ht="39">
+    <row r="2" spans="1:15" ht="19.5">
       <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
@@ -10328,14 +10821,14 @@
         <v>9</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" s="20"/>
       <c r="I2" s="48"/>
     </row>
     <row r="3" spans="1:15" ht="26.25" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -10455,7 +10948,7 @@
     </row>
     <row r="11" spans="1:15" ht="26.25" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
@@ -10470,7 +10963,7 @@
     </row>
     <row r="12" spans="1:15" ht="26.25" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -10485,7 +10978,7 @@
     </row>
     <row r="13" spans="1:15" ht="26.25" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -10495,7 +10988,7 @@
       <c r="G13" s="22"/>
       <c r="L13" s="28"/>
       <c r="O13" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="30.75" customHeight="1">
@@ -10510,7 +11003,7 @@
       <c r="G14" s="22"/>
       <c r="L14" s="28"/>
       <c r="O14" s="18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="26.25" customHeight="1">
@@ -10525,7 +11018,7 @@
       <c r="G15" s="22"/>
       <c r="L15" s="31"/>
       <c r="O15" s="18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="26.25" customHeight="1">
@@ -10815,7 +11308,7 @@
     </row>
     <row r="35" spans="1:15" ht="26.25" customHeight="1">
       <c r="A35" s="36" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B35" s="22"/>
       <c r="C35" s="15"/>
@@ -10830,7 +11323,7 @@
     </row>
     <row r="36" spans="1:15" ht="26.25" customHeight="1">
       <c r="A36" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="15"/>
@@ -10845,7 +11338,7 @@
     </row>
     <row r="37" spans="1:15" ht="15.75" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="15"/>
@@ -10860,7 +11353,7 @@
     </row>
     <row r="38" spans="1:15" ht="15.75" customHeight="1">
       <c r="A38" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="15"/>
@@ -10875,7 +11368,7 @@
     </row>
     <row r="39" spans="1:15" ht="15.75" customHeight="1">
       <c r="A39" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="15"/>
@@ -10890,7 +11383,7 @@
     </row>
     <row r="40" spans="1:15" ht="15.75" customHeight="1">
       <c r="A40" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B40" s="16"/>
       <c r="C40" s="15"/>
@@ -10905,7 +11398,7 @@
     </row>
     <row r="41" spans="1:15" ht="15.75" customHeight="1">
       <c r="A41" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B41" s="16"/>
       <c r="C41" s="15"/>
@@ -10929,21 +11422,21 @@
       <c r="F43" s="52"/>
       <c r="L43" s="28"/>
       <c r="O43" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="15.75" customHeight="1">
       <c r="F44" s="52"/>
       <c r="L44" s="31"/>
       <c r="O44" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="15.75" customHeight="1">
       <c r="F45" s="52"/>
       <c r="L45" s="31"/>
       <c r="O45" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="15.75" customHeight="1">
@@ -10957,21 +11450,21 @@
       <c r="F47" s="52"/>
       <c r="L47" s="24"/>
       <c r="O47" s="18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="15.75" customHeight="1">
       <c r="F48" s="52"/>
       <c r="L48" s="24"/>
       <c r="O48" s="18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="3:15" ht="15.75" customHeight="1">
       <c r="F49" s="52"/>
       <c r="L49" s="39"/>
       <c r="O49" s="18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50" spans="3:15" ht="15.75" customHeight="1">
@@ -10985,49 +11478,49 @@
       <c r="F51" s="52"/>
       <c r="L51" s="39"/>
       <c r="O51" s="18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="3:15" ht="15.75" customHeight="1">
       <c r="F52" s="52"/>
       <c r="L52" s="24"/>
       <c r="O52" s="18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="3:15" ht="15.75" customHeight="1">
       <c r="F53" s="52"/>
       <c r="L53" s="24"/>
       <c r="O53" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54" spans="3:15" ht="15.75" customHeight="1">
       <c r="F54" s="52"/>
       <c r="L54" s="24"/>
       <c r="O54" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="3:15" ht="15.75" customHeight="1">
       <c r="F55" s="52"/>
       <c r="L55" s="39"/>
       <c r="O55" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="3:15" ht="15.75" customHeight="1">
       <c r="F56" s="52"/>
       <c r="L56" s="39"/>
       <c r="O56" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="3:15" ht="15.75" customHeight="1">
       <c r="F57" s="52"/>
       <c r="L57" s="24"/>
       <c r="O57" s="18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="3:15" ht="15.75" customHeight="1">
@@ -11035,7 +11528,7 @@
       <c r="F58" s="52"/>
       <c r="L58" s="24"/>
       <c r="O58" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="3:15" ht="15.75" customHeight="1">
@@ -11056,244 +11549,244 @@
       <c r="F61" s="52"/>
       <c r="L61" s="24"/>
       <c r="O61" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="3:15" ht="15.75" customHeight="1">
       <c r="F62" s="52"/>
       <c r="L62" s="24"/>
       <c r="O62" s="18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="3:15" ht="15.75" customHeight="1">
       <c r="F63" s="52"/>
       <c r="L63" s="24"/>
       <c r="O63" s="18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="64" spans="3:15" ht="15.75" customHeight="1">
       <c r="F64" s="52"/>
       <c r="L64" s="24"/>
       <c r="O64" s="18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="6:15" ht="15.75" customHeight="1">
       <c r="F65" s="52"/>
       <c r="L65" s="24"/>
       <c r="O65" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="6:15" ht="15.75" customHeight="1">
       <c r="F66" s="52"/>
       <c r="L66" s="24"/>
       <c r="O66" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="67" spans="6:15" ht="15.75" customHeight="1">
       <c r="F67" s="52"/>
       <c r="L67" s="24"/>
       <c r="O67" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="68" spans="6:15" ht="15.75" customHeight="1">
       <c r="F68" s="52"/>
       <c r="L68" s="24"/>
       <c r="O68" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69" spans="6:15" ht="15.75" customHeight="1">
       <c r="F69" s="52"/>
       <c r="L69" s="24"/>
       <c r="O69" s="18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="6:15" ht="15.75" customHeight="1">
       <c r="F70" s="52"/>
       <c r="L70" s="24"/>
       <c r="O70" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="71" spans="6:15" ht="15.75" customHeight="1">
       <c r="F71" s="52"/>
       <c r="L71" s="24"/>
       <c r="O71" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="6:15" ht="15.75" customHeight="1">
       <c r="F72" s="52"/>
       <c r="L72" s="24"/>
       <c r="O72" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73" spans="6:15" ht="15.75" customHeight="1">
       <c r="F73" s="52"/>
       <c r="L73" s="24"/>
       <c r="O73" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="74" spans="6:15" ht="15.75" customHeight="1">
       <c r="F74" s="52"/>
       <c r="L74" s="24"/>
       <c r="O74" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="75" spans="6:15" ht="15.75" customHeight="1">
       <c r="F75" s="52"/>
       <c r="L75" s="24"/>
       <c r="O75" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="76" spans="6:15" ht="15.75" customHeight="1">
       <c r="F76" s="52"/>
       <c r="L76" s="24"/>
       <c r="O76" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="77" spans="6:15" ht="15.75" customHeight="1">
       <c r="F77" s="52"/>
       <c r="L77" s="24"/>
       <c r="O77" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="78" spans="6:15" ht="15.75" customHeight="1">
       <c r="F78" s="52"/>
       <c r="L78" s="24"/>
       <c r="O78" s="18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="79" spans="6:15" ht="15.75" customHeight="1">
       <c r="F79" s="52"/>
       <c r="L79" s="24"/>
       <c r="O79" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="80" spans="6:15" ht="15.75" customHeight="1">
       <c r="F80" s="52"/>
       <c r="L80" s="24"/>
       <c r="O80" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="81" spans="6:15" ht="15.75" customHeight="1">
       <c r="F81" s="52"/>
       <c r="L81" s="24"/>
       <c r="O81" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="82" spans="6:15" ht="15.75" customHeight="1">
       <c r="F82" s="52"/>
       <c r="L82" s="24"/>
       <c r="O82" s="18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="83" spans="6:15" ht="15.75" customHeight="1">
       <c r="F83" s="52"/>
       <c r="O83" s="18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="84" spans="6:15" ht="15.75" customHeight="1">
       <c r="F84" s="52"/>
       <c r="O84" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="85" spans="6:15" ht="15.75" customHeight="1">
       <c r="F85" s="52"/>
       <c r="O85" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="86" spans="6:15" ht="15.75" customHeight="1">
       <c r="F86" s="52"/>
       <c r="O86" s="18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="87" spans="6:15" ht="15.75" customHeight="1">
       <c r="F87" s="52"/>
       <c r="O87" s="18" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="88" spans="6:15" ht="15.75" customHeight="1">
       <c r="F88" s="52"/>
       <c r="O88" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="89" spans="6:15" ht="15.75" customHeight="1">
       <c r="F89" s="52"/>
       <c r="O89" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="90" spans="6:15" ht="15.75" customHeight="1">
       <c r="F90" s="52"/>
       <c r="O90" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="91" spans="6:15" ht="15.75" customHeight="1">
       <c r="F91" s="52"/>
       <c r="O91" s="18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="92" spans="6:15" ht="15.75" customHeight="1">
       <c r="F92" s="52"/>
       <c r="O92" s="18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="93" spans="6:15" ht="15.75" customHeight="1">
       <c r="F93" s="52"/>
       <c r="O93" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="94" spans="6:15" ht="15.75" customHeight="1">
       <c r="F94" s="52"/>
       <c r="O94" s="18" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="95" spans="6:15" ht="15.75" customHeight="1">
       <c r="F95" s="52"/>
       <c r="O95" s="18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="96" spans="6:15" ht="15.75" customHeight="1">
       <c r="F96" s="52"/>
       <c r="O96" s="18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="97" spans="6:15" ht="15.75" customHeight="1">
       <c r="F97" s="52"/>
       <c r="O97" s="18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="98" spans="6:15" ht="15.75" customHeight="1">
@@ -11318,7 +11811,7 @@
       <c r="F101" s="52"/>
       <c r="L101" s="23"/>
       <c r="O101" s="18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="102" spans="6:15" ht="15.75" customHeight="1">
@@ -11332,7 +11825,7 @@
       <c r="F103" s="52"/>
       <c r="L103" s="24"/>
       <c r="O103" s="18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="104" spans="6:15" ht="15.75" customHeight="1">
@@ -11353,7 +11846,7 @@
       <c r="F106" s="52"/>
       <c r="L106" s="39"/>
       <c r="O106" s="18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107" spans="6:15" ht="15.75" customHeight="1">
@@ -11367,7 +11860,7 @@
       <c r="F108" s="52"/>
       <c r="L108" s="39"/>
       <c r="O108" s="18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="109" spans="6:15" ht="15.75" customHeight="1">
@@ -11381,14 +11874,14 @@
       <c r="F110" s="52"/>
       <c r="L110" s="24"/>
       <c r="O110" s="18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="111" spans="6:15" ht="15.75" customHeight="1">
       <c r="F111" s="52"/>
       <c r="L111" s="24"/>
       <c r="O111" s="18" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="112" spans="6:15" ht="15.75" customHeight="1">
@@ -11402,49 +11895,49 @@
       <c r="F113" s="52"/>
       <c r="L113" s="39"/>
       <c r="O113" s="18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="114" spans="6:15" ht="15.75" customHeight="1">
       <c r="F114" s="52"/>
       <c r="L114" s="39"/>
       <c r="O114" s="18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="115" spans="6:15" ht="15.75" customHeight="1">
       <c r="F115" s="52"/>
       <c r="L115" s="39"/>
       <c r="O115" s="18" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="116" spans="6:15" ht="15.75" customHeight="1">
       <c r="F116" s="52"/>
       <c r="L116" s="24"/>
       <c r="O116" s="18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="117" spans="6:15" ht="15.75" customHeight="1">
       <c r="F117" s="52"/>
       <c r="L117" s="24"/>
       <c r="O117" s="18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="118" spans="6:15" ht="15.75" customHeight="1">
       <c r="F118" s="52"/>
       <c r="L118" s="39"/>
       <c r="O118" s="18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="119" spans="6:15" ht="15.75" customHeight="1">
       <c r="F119" s="52"/>
       <c r="L119" s="39"/>
       <c r="O119" s="18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="120" spans="6:15" ht="15.75" customHeight="1">
@@ -11458,49 +11951,49 @@
       <c r="F121" s="52"/>
       <c r="L121" s="24"/>
       <c r="O121" s="18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="122" spans="6:15" ht="15.75" customHeight="1">
       <c r="F122" s="52"/>
       <c r="L122" s="24"/>
       <c r="O122" s="18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="123" spans="6:15" ht="15.75" customHeight="1">
       <c r="F123" s="52"/>
       <c r="L123" s="24"/>
       <c r="O123" s="18" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="124" spans="6:15" ht="15.75" customHeight="1">
       <c r="F124" s="52"/>
       <c r="L124" s="24"/>
       <c r="O124" s="18" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="125" spans="6:15" ht="15.75" customHeight="1">
       <c r="F125" s="52"/>
       <c r="L125" s="24"/>
       <c r="O125" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="126" spans="6:15" ht="15.75" customHeight="1">
       <c r="F126" s="52"/>
       <c r="L126" s="24"/>
       <c r="O126" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="127" spans="6:15" ht="15.75" customHeight="1">
       <c r="F127" s="52"/>
       <c r="L127" s="39"/>
       <c r="O127" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="128" spans="6:15" ht="15.75" customHeight="1">
@@ -12887,10 +13380,10 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57" t="s">
-        <v>197</v>
-      </c>
-      <c r="C1" s="58"/>
+      <c r="B1" s="75" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1" s="76"/>
       <c r="D1" s="7">
         <v>46270</v>
       </c>
@@ -12902,7 +13395,7 @@
       <c r="J1" s="51"/>
       <c r="K1" s="51"/>
     </row>
-    <row r="2" spans="1:15" ht="39">
+    <row r="2" spans="1:15" ht="19.5">
       <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
@@ -12922,7 +13415,7 @@
         <v>9</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" s="51"/>
       <c r="I2" s="51"/>
@@ -12931,7 +13424,7 @@
     </row>
     <row r="3" spans="1:15" ht="26.25" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -13077,7 +13570,7 @@
     </row>
     <row r="11" spans="1:15" ht="26.25" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
@@ -13096,7 +13589,7 @@
     </row>
     <row r="12" spans="1:15" ht="26.25" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -13115,7 +13608,7 @@
     </row>
     <row r="13" spans="1:15" ht="26.25" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -13129,7 +13622,7 @@
       <c r="K13" s="51"/>
       <c r="L13" s="28"/>
       <c r="O13" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="26.25" customHeight="1">
@@ -13148,7 +13641,7 @@
       <c r="K14" s="51"/>
       <c r="L14" s="28"/>
       <c r="O14" s="18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="26.25" customHeight="1">
@@ -13167,7 +13660,7 @@
       <c r="K15" s="51"/>
       <c r="L15" s="28"/>
       <c r="O15" s="18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="26.25" customHeight="1">
@@ -13521,7 +14014,7 @@
     </row>
     <row r="35" spans="1:15" ht="26.25" customHeight="1">
       <c r="A35" s="36" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B35" s="22"/>
       <c r="C35" s="15"/>
@@ -13536,7 +14029,7 @@
     </row>
     <row r="36" spans="1:15" ht="25.5" customHeight="1">
       <c r="A36" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="15"/>
@@ -13551,7 +14044,7 @@
     </row>
     <row r="37" spans="1:15" ht="15.75" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="15"/>
@@ -13566,7 +14059,7 @@
     </row>
     <row r="38" spans="1:15" ht="15.75" customHeight="1">
       <c r="A38" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="15"/>
@@ -13581,7 +14074,7 @@
     </row>
     <row r="39" spans="1:15" ht="15.75" customHeight="1">
       <c r="A39" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="15"/>
@@ -13596,7 +14089,7 @@
     </row>
     <row r="40" spans="1:15" ht="15.75" customHeight="1">
       <c r="A40" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B40" s="16"/>
       <c r="C40" s="15"/>
@@ -13611,7 +14104,7 @@
     </row>
     <row r="41" spans="1:15" ht="15.75" customHeight="1">
       <c r="A41" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B41" s="16"/>
       <c r="C41" s="15"/>
@@ -13633,19 +14126,19 @@
     <row r="43" spans="1:15" ht="15.75" customHeight="1">
       <c r="L43" s="28"/>
       <c r="O43" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="15.75" customHeight="1">
       <c r="L44" s="28"/>
       <c r="O44" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="15.75" customHeight="1">
       <c r="L45" s="28"/>
       <c r="O45" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="15.75" customHeight="1">
@@ -13657,19 +14150,19 @@
     <row r="47" spans="1:15" ht="15.75" customHeight="1">
       <c r="L47" s="24"/>
       <c r="O47" s="18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="15.75" customHeight="1">
       <c r="L48" s="24"/>
       <c r="O48" s="18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="12:15" ht="15.75" customHeight="1">
       <c r="L49" s="39"/>
       <c r="O49" s="18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50" spans="12:15" ht="15.75" customHeight="1">
@@ -13681,49 +14174,49 @@
     <row r="51" spans="12:15" ht="15.75" customHeight="1">
       <c r="L51" s="39"/>
       <c r="O51" s="18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="12:15" ht="15.75" customHeight="1">
       <c r="L52" s="24"/>
       <c r="O52" s="18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="12:15" ht="15.75" customHeight="1">
       <c r="L53" s="24"/>
       <c r="O53" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54" spans="12:15" ht="15.75" customHeight="1">
       <c r="L54" s="24"/>
       <c r="O54" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="12:15" ht="15.75" customHeight="1">
       <c r="L55" s="39"/>
       <c r="O55" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="12:15" ht="15.75" customHeight="1">
       <c r="L56" s="39"/>
       <c r="O56" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="12:15" ht="15.75" customHeight="1">
       <c r="L57" s="24"/>
       <c r="O57" s="18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="12:15" ht="15.75" customHeight="1">
       <c r="L58" s="24"/>
       <c r="O58" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="12:15" ht="15.75" customHeight="1">
@@ -13741,208 +14234,208 @@
     <row r="61" spans="12:15" ht="15.75" customHeight="1">
       <c r="L61" s="24"/>
       <c r="O61" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="12:15" ht="15.75" customHeight="1">
       <c r="L62" s="24"/>
       <c r="O62" s="18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="12:15" ht="15.75" customHeight="1">
       <c r="L63" s="24"/>
       <c r="O63" s="18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="64" spans="12:15" ht="15.75" customHeight="1">
       <c r="L64" s="24"/>
       <c r="O64" s="18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="12:15" ht="15.75" customHeight="1">
       <c r="L65" s="24"/>
       <c r="O65" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="12:15" ht="15.75" customHeight="1">
       <c r="L66" s="24"/>
       <c r="O66" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="67" spans="12:15" ht="15.75" customHeight="1">
       <c r="L67" s="24"/>
       <c r="O67" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="68" spans="12:15" ht="15.75" customHeight="1">
       <c r="L68" s="24"/>
       <c r="O68" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69" spans="12:15" ht="15.75" customHeight="1">
       <c r="L69" s="24"/>
       <c r="O69" s="18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="12:15" ht="15.75" customHeight="1">
       <c r="L70" s="24"/>
       <c r="O70" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="71" spans="12:15" ht="15.75" customHeight="1">
       <c r="L71" s="24"/>
       <c r="O71" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="12:15" ht="15.75" customHeight="1">
       <c r="L72" s="24"/>
       <c r="O72" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73" spans="12:15" ht="15.75" customHeight="1">
       <c r="L73" s="24"/>
       <c r="O73" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="74" spans="12:15" ht="15.75" customHeight="1">
       <c r="L74" s="24"/>
       <c r="O74" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="75" spans="12:15" ht="15.75" customHeight="1">
       <c r="L75" s="24"/>
       <c r="O75" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="76" spans="12:15" ht="15.75" customHeight="1">
       <c r="L76" s="24"/>
       <c r="O76" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="77" spans="12:15" ht="15.75" customHeight="1">
       <c r="L77" s="24"/>
       <c r="O77" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="78" spans="12:15" ht="15.75" customHeight="1">
       <c r="L78" s="24"/>
       <c r="O78" s="18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="79" spans="12:15" ht="15.75" customHeight="1">
       <c r="L79" s="24"/>
       <c r="O79" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="80" spans="12:15" ht="15.75" customHeight="1">
       <c r="L80" s="24"/>
       <c r="O80" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="81" spans="12:15" ht="15.75" customHeight="1">
       <c r="L81" s="24"/>
       <c r="O81" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="82" spans="12:15" ht="15.75" customHeight="1">
       <c r="L82" s="24"/>
       <c r="O82" s="18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="83" spans="12:15" ht="15.75" customHeight="1">
       <c r="O83" s="18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="84" spans="12:15" ht="15.75" customHeight="1">
       <c r="O84" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="85" spans="12:15" ht="15.75" customHeight="1">
       <c r="O85" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="86" spans="12:15" ht="15.75" customHeight="1">
       <c r="O86" s="18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="87" spans="12:15" ht="15.75" customHeight="1">
       <c r="O87" s="18" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="88" spans="12:15" ht="15.75" customHeight="1">
       <c r="O88" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="89" spans="12:15" ht="15.75" customHeight="1">
       <c r="O89" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="90" spans="12:15" ht="15.75" customHeight="1">
       <c r="O90" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="91" spans="12:15" ht="15.75" customHeight="1">
       <c r="O91" s="18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="92" spans="12:15" ht="15.75" customHeight="1">
       <c r="O92" s="18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="93" spans="12:15" ht="15.75" customHeight="1">
       <c r="O93" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="94" spans="12:15" ht="15.75" customHeight="1">
       <c r="O94" s="18" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="95" spans="12:15" ht="15.75" customHeight="1">
       <c r="O95" s="18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="96" spans="12:15" ht="15.75" customHeight="1">
       <c r="O96" s="18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="97" spans="12:15" ht="15.75" customHeight="1">
       <c r="O97" s="18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="98" spans="12:15" ht="15.75" customHeight="1">
@@ -13963,7 +14456,7 @@
     <row r="101" spans="12:15" ht="15.75" customHeight="1">
       <c r="L101" s="23"/>
       <c r="O101" s="18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="102" spans="12:15" ht="15.75" customHeight="1">
@@ -13975,7 +14468,7 @@
     <row r="103" spans="12:15" ht="15.75" customHeight="1">
       <c r="L103" s="24"/>
       <c r="O103" s="18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="104" spans="12:15" ht="15.75" customHeight="1">
@@ -13993,7 +14486,7 @@
     <row r="106" spans="12:15" ht="15.75" customHeight="1">
       <c r="L106" s="39"/>
       <c r="O106" s="18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107" spans="12:15" ht="15.75" customHeight="1">
@@ -14005,7 +14498,7 @@
     <row r="108" spans="12:15" ht="15.75" customHeight="1">
       <c r="L108" s="39"/>
       <c r="O108" s="18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="109" spans="12:15" ht="15.75" customHeight="1">
@@ -14017,13 +14510,13 @@
     <row r="110" spans="12:15" ht="15.75" customHeight="1">
       <c r="L110" s="24"/>
       <c r="O110" s="18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="111" spans="12:15" ht="15.75" customHeight="1">
       <c r="L111" s="24"/>
       <c r="O111" s="18" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="112" spans="12:15" ht="15.75" customHeight="1">
@@ -14035,43 +14528,43 @@
     <row r="113" spans="12:15" ht="15.75" customHeight="1">
       <c r="L113" s="39"/>
       <c r="O113" s="18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="114" spans="12:15" ht="15.75" customHeight="1">
       <c r="L114" s="39"/>
       <c r="O114" s="18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="115" spans="12:15" ht="15.75" customHeight="1">
       <c r="L115" s="39"/>
       <c r="O115" s="18" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="116" spans="12:15" ht="15.75" customHeight="1">
       <c r="L116" s="24"/>
       <c r="O116" s="18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="117" spans="12:15" ht="15.75" customHeight="1">
       <c r="L117" s="24"/>
       <c r="O117" s="18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="118" spans="12:15" ht="15.75" customHeight="1">
       <c r="L118" s="39"/>
       <c r="O118" s="18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="119" spans="12:15" ht="15.75" customHeight="1">
       <c r="L119" s="39"/>
       <c r="O119" s="18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="120" spans="12:15" ht="15.75" customHeight="1">
@@ -14083,49 +14576,49 @@
     <row r="121" spans="12:15" ht="15.75" customHeight="1">
       <c r="L121" s="24"/>
       <c r="O121" s="18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="122" spans="12:15" ht="15.75" customHeight="1">
       <c r="L122" s="24"/>
       <c r="O122" s="18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="123" spans="12:15" ht="15.75" customHeight="1">
       <c r="L123" s="24"/>
       <c r="O123" s="18" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="124" spans="12:15" ht="15.75" customHeight="1">
       <c r="L124" s="24"/>
       <c r="O124" s="18" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="125" spans="12:15" ht="15.75" customHeight="1">
       <c r="L125" s="24"/>
       <c r="O125" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="126" spans="12:15" ht="15.75" customHeight="1">
       <c r="L126" s="24"/>
       <c r="O126" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="127" spans="12:15" ht="15.75" customHeight="1">
       <c r="L127" s="39"/>
       <c r="O127" s="54" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="128" spans="12:15" ht="15.75" customHeight="1">
       <c r="L128" s="39"/>
       <c r="O128" s="33" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="129" spans="12:12" ht="15.75" customHeight="1">

--- a/Расписание.xlsx
+++ b/Расписание.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1961" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1958" uniqueCount="344">
   <si>
     <t>ТОЛЬКО ПОНЕДЕЛЬНИК!!!</t>
   </si>
@@ -849,10 +849,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Классный час /104</t>
-  </si>
-  <si>
-    <t>Русский язык/233</t>
+    <t>Обществознание/423</t>
   </si>
   <si>
     <r>
@@ -875,133 +872,70 @@
     </r>
   </si>
   <si>
-    <t>Классный час /318</t>
-  </si>
-  <si>
-    <t>Классный час /233</t>
-  </si>
-  <si>
-    <t>Классный час /301</t>
-  </si>
-  <si>
-    <t>Классный час /405</t>
-  </si>
-  <si>
-    <t>Классный час /400</t>
-  </si>
-  <si>
-    <t>Классный час /300</t>
-  </si>
-  <si>
-    <t>Классный час /317</t>
-  </si>
-  <si>
-    <t>Классный час /421</t>
-  </si>
-  <si>
-    <t>Классный час /406</t>
-  </si>
-  <si>
-    <t>Классный час /308</t>
-  </si>
-  <si>
-    <t>Классный час /401</t>
-  </si>
-  <si>
-    <t>Классный час /201</t>
-  </si>
-  <si>
-    <t>Русский язык/421</t>
-  </si>
-  <si>
-    <t>Классный час /327</t>
-  </si>
-  <si>
-    <t>Классный час / 312</t>
-  </si>
-  <si>
-    <t>ОТГ/101</t>
-  </si>
-  <si>
-    <t>Материалов/104</t>
-  </si>
-  <si>
-    <t>Классный час / 404</t>
-  </si>
-  <si>
-    <t>Эл.матер.вед./317</t>
-  </si>
-  <si>
-    <t>Классный час / 318</t>
-  </si>
-  <si>
-    <t>Эл.тех./301</t>
-  </si>
-  <si>
-    <t>Классный час /411</t>
-  </si>
-  <si>
-    <t>Классный час /423</t>
-  </si>
-  <si>
-    <t>Классный час /419</t>
-  </si>
-  <si>
-    <t>Классный час /416</t>
-  </si>
-  <si>
-    <t>Классный час /418</t>
-  </si>
-  <si>
-    <t>Информат./400</t>
-  </si>
-  <si>
-    <t>Классный час /312</t>
-  </si>
-  <si>
-    <t>Материалов./104</t>
-  </si>
-  <si>
-    <t>Классный час /228</t>
-  </si>
-  <si>
-    <t>Классный час /310</t>
-  </si>
-  <si>
-    <t>ПМ 06/304</t>
-  </si>
-  <si>
-    <t>ПМ04/416</t>
-  </si>
-  <si>
-    <t>Классный час /231</t>
-  </si>
-  <si>
-    <t>Классный час /227</t>
-  </si>
-  <si>
-    <t>ПМ 03/231</t>
-  </si>
-  <si>
-    <t>ПМ 01/233</t>
-  </si>
-  <si>
-    <t>Охрана труда/418</t>
-  </si>
-  <si>
-    <t>ПМ03/201</t>
-  </si>
-  <si>
-    <t>ПМ03/423</t>
-  </si>
-  <si>
-    <t>Классный час /304</t>
-  </si>
-  <si>
-    <t>Классный час /404</t>
-  </si>
-  <si>
-    <t>ПМ 01/300</t>
+    <t>Информатика/226</t>
+  </si>
+  <si>
+    <t>Ин.яз./312/411</t>
+  </si>
+  <si>
+    <t>Физика/104</t>
+  </si>
+  <si>
+    <t>Ин.яз./411</t>
+  </si>
+  <si>
+    <t>Русский язык/406</t>
+  </si>
+  <si>
+    <t>Материаловед./104</t>
+  </si>
+  <si>
+    <t>Эл.тех./310 (С)</t>
+  </si>
+  <si>
+    <t>Материаловед./310</t>
+  </si>
+  <si>
+    <t>Иностр.яз./312/314</t>
+  </si>
+  <si>
+    <t>Эл.тех./300</t>
+  </si>
+  <si>
+    <t>Культура речи/423</t>
+  </si>
+  <si>
+    <t>Охрана труда/300</t>
+  </si>
+  <si>
+    <t>ПМ 01/401 (Ш)</t>
+  </si>
+  <si>
+    <t>ПМ 02/416 (Т)</t>
+  </si>
+  <si>
+    <t>ПМ 01/309 (М)</t>
+  </si>
+  <si>
+    <t>ПМ 06/305</t>
+  </si>
+  <si>
+    <t>ПМ 04/327</t>
+  </si>
+  <si>
+    <t>Кар.мод./304 (С)</t>
+  </si>
+  <si>
+    <t>Психология/406</t>
+  </si>
+  <si>
+    <t>ПМ 02/309 (М)</t>
+  </si>
+  <si>
+    <t>Прав. основы ПД/304</t>
+  </si>
+  <si>
+    <t>Психология/423</t>
   </si>
   <si>
     <r>
@@ -1030,15 +964,18 @@
     <t>Обществозн/411</t>
   </si>
   <si>
-    <t>Физика/104</t>
-  </si>
-  <si>
     <t>Иностран. язык/312</t>
   </si>
   <si>
+    <t>Материалов./104</t>
+  </si>
+  <si>
     <t>Материалов./317</t>
   </si>
   <si>
+    <t>Эл.тех./301</t>
+  </si>
+  <si>
     <t>Ин. яз/312/314</t>
   </si>
   <si>
@@ -1048,12 +985,15 @@
     <t>Материалов./411</t>
   </si>
   <si>
-    <t>Материаловед./104</t>
-  </si>
-  <si>
     <t>Осн. фин. гр/418</t>
   </si>
   <si>
+    <t>ПМ03/423</t>
+  </si>
+  <si>
+    <t>ПМ 06/304</t>
+  </si>
+  <si>
     <t>ПМ 01/300(М)</t>
   </si>
   <si>
@@ -1061,6 +1001,9 @@
   </si>
   <si>
     <t>Осн. экон/418</t>
+  </si>
+  <si>
+    <t>ПМ 03/231</t>
   </si>
   <si>
     <t>ПМ 02/300(М)</t>
@@ -1104,13 +1047,10 @@
     <t>Ин.яз./312/314</t>
   </si>
   <si>
-    <t>Эл.тех./300</t>
+    <t>ПМ04/416</t>
   </si>
   <si>
     <t>ПМ03/414</t>
-  </si>
-  <si>
-    <t>Психология/423</t>
   </si>
   <si>
     <t>Психология/411</t>
@@ -1142,9 +1082,6 @@
     <t>ОБЗР/310 (В)</t>
   </si>
   <si>
-    <t>Информатика/226</t>
-  </si>
-  <si>
     <t>ОБЗР/310</t>
   </si>
   <si>
@@ -1152,9 +1089,6 @@
   </si>
   <si>
     <t>Эл.техника/300</t>
-  </si>
-  <si>
-    <t>Материаловед./310</t>
   </si>
   <si>
     <t>Прав.основы ПД/304</t>
@@ -1193,9 +1127,6 @@
   </si>
   <si>
     <t>Иностр.яз./410</t>
-  </si>
-  <si>
-    <t>Иностр.яз./312/314</t>
   </si>
   <si>
     <t>Электротехника/310</t>
@@ -1856,7 +1787,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="167">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2244,9 +2175,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="43" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="10" fontId="29" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="37" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="44" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -3773,7 +3701,7 @@
       </c>
       <c r="AJ18" s="34" t="str">
         <f>'ВТОРНИК'!B36</f>
-        <v>Классный час /400</v>
+        <v>Психология/406</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
@@ -3915,7 +3843,7 @@
       </c>
       <c r="AJ19" s="34" t="str">
         <f>'ВТОРНИК'!C36</f>
-        <v>ПМ03/423</v>
+        <v>ПМ 02/309 (М)</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
@@ -4057,13 +3985,13 @@
       </c>
       <c r="AJ20" s="34" t="str">
         <f>'ВТОРНИК'!D36</f>
-        <v>ПМ 01/301</v>
+        <v>Прав. основы ПД/304</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="37" t="str">
         <f>'ВТОРНИК'!D1</f>
-        <v>01.09.2026</v>
+        <v>08.09.2026</v>
       </c>
       <c r="B21" s="33">
         <v>4.0</v>
@@ -4736,7 +4664,7 @@
       </c>
       <c r="AJ25" s="34" t="str">
         <f>'ВТОРНИК'!C36</f>
-        <v>ПМ03/423</v>
+        <v>ПМ 02/309 (М)</v>
       </c>
     </row>
     <row r="26" ht="15.0" customHeight="1">
@@ -7347,7 +7275,7 @@
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="37" t="str">
         <f>'СУББОТА'!D1</f>
-        <v>05.09.2026</v>
+        <v>06.06.2026</v>
       </c>
       <c r="B45" s="33">
         <v>4.0</v>
@@ -9731,7 +9659,7 @@
     <col customWidth="1" min="4" max="4" width="36.14"/>
     <col customWidth="1" min="5" max="5" width="32.29"/>
     <col customWidth="1" min="6" max="6" width="30.57"/>
-    <col customWidth="1" min="7" max="7" width="30.14"/>
+    <col customWidth="1" min="7" max="7" width="32.43"/>
     <col customWidth="1" min="8" max="12" width="8.71"/>
     <col customWidth="1" min="13" max="13" width="27.0"/>
     <col customWidth="1" min="14" max="17" width="8.71"/>
@@ -9747,7 +9675,7 @@
       </c>
       <c r="C1" s="111"/>
       <c r="D1" s="112">
-        <v>46266.0</v>
+        <v>46273.0</v>
       </c>
       <c r="E1" s="113"/>
       <c r="F1" s="114"/>
@@ -9781,13 +9709,13 @@
         <v>74</v>
       </c>
       <c r="B3" s="118" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="118" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" s="118" t="s">
         <v>271</v>
-      </c>
-      <c r="C3" s="118" t="s">
-        <v>272</v>
-      </c>
-      <c r="D3" s="118" t="s">
-        <v>132</v>
       </c>
       <c r="E3" s="118"/>
       <c r="F3" s="119"/>
@@ -9798,16 +9726,16 @@
     </row>
     <row r="4" ht="26.25" customHeight="1">
       <c r="A4" s="117" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B4" s="118" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C4" s="118" t="s">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="D4" s="118" t="s">
-        <v>272</v>
+        <v>104</v>
       </c>
       <c r="E4" s="118"/>
       <c r="F4" s="119"/>
@@ -9821,10 +9749,10 @@
         <v>82</v>
       </c>
       <c r="B5" s="118" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C5" s="118" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D5" s="118" t="s">
         <v>87</v>
@@ -9841,13 +9769,13 @@
         <v>86</v>
       </c>
       <c r="B6" s="118" t="s">
-        <v>276</v>
+        <v>204</v>
       </c>
       <c r="C6" s="118" t="s">
         <v>87</v>
       </c>
       <c r="D6" s="118" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E6" s="118"/>
       <c r="F6" s="118"/>
@@ -9861,7 +9789,7 @@
         <v>89</v>
       </c>
       <c r="B7" s="118" t="s">
-        <v>277</v>
+        <v>87</v>
       </c>
       <c r="C7" s="118" t="s">
         <v>76</v>
@@ -9881,7 +9809,7 @@
         <v>92</v>
       </c>
       <c r="B8" s="118" t="s">
-        <v>278</v>
+        <v>113</v>
       </c>
       <c r="C8" s="118" t="s">
         <v>84</v>
@@ -9901,13 +9829,13 @@
         <v>95</v>
       </c>
       <c r="B9" s="118" t="s">
-        <v>279</v>
+        <v>93</v>
       </c>
       <c r="C9" s="118" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D9" s="118" t="s">
-        <v>85</v>
+        <v>274</v>
       </c>
       <c r="E9" s="118"/>
       <c r="F9" s="118"/>
@@ -9922,13 +9850,13 @@
         <v>99</v>
       </c>
       <c r="B10" s="118" t="s">
-        <v>280</v>
+        <v>83</v>
       </c>
       <c r="C10" s="118" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="118" t="s">
         <v>85</v>
-      </c>
-      <c r="D10" s="118" t="s">
-        <v>83</v>
       </c>
       <c r="E10" s="118"/>
       <c r="F10" s="127"/>
@@ -9943,13 +9871,13 @@
         <v>101</v>
       </c>
       <c r="B11" s="118" t="s">
-        <v>281</v>
+        <v>85</v>
       </c>
       <c r="C11" s="118" t="s">
         <v>93</v>
       </c>
       <c r="D11" s="118" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E11" s="118"/>
       <c r="F11" s="118"/>
@@ -9964,10 +9892,10 @@
         <v>103</v>
       </c>
       <c r="B12" s="118" t="s">
-        <v>282</v>
+        <v>104</v>
       </c>
       <c r="C12" s="118" t="s">
-        <v>90</v>
+        <v>274</v>
       </c>
       <c r="D12" s="118" t="s">
         <v>93</v>
@@ -9985,13 +9913,13 @@
         <v>106</v>
       </c>
       <c r="B13" s="118" t="s">
-        <v>283</v>
+        <v>76</v>
       </c>
       <c r="C13" s="118" t="s">
-        <v>77</v>
+        <v>275</v>
       </c>
       <c r="D13" s="118" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E13" s="118"/>
       <c r="F13" s="118"/>
@@ -10006,13 +9934,13 @@
         <v>109</v>
       </c>
       <c r="B14" s="118" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="C14" s="118" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="D14" s="118" t="s">
-        <v>77</v>
+        <v>275</v>
       </c>
       <c r="E14" s="131"/>
       <c r="F14" s="118"/>
@@ -10027,13 +9955,13 @@
         <v>112</v>
       </c>
       <c r="B15" s="118" t="s">
-        <v>285</v>
+        <v>84</v>
       </c>
       <c r="C15" s="133" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="D15" s="133" t="s">
-        <v>204</v>
+        <v>255</v>
       </c>
       <c r="E15" s="118"/>
       <c r="F15" s="118"/>
@@ -10048,13 +9976,13 @@
         <v>115</v>
       </c>
       <c r="B16" s="118" t="s">
-        <v>287</v>
+        <v>96</v>
       </c>
       <c r="C16" s="133" t="s">
-        <v>204</v>
+        <v>255</v>
       </c>
       <c r="D16" s="133" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E16" s="118"/>
       <c r="F16" s="133"/>
@@ -10071,14 +9999,14 @@
       <c r="B17" s="133"/>
       <c r="C17" s="133"/>
       <c r="D17" s="133"/>
-      <c r="E17" s="118" t="s">
-        <v>288</v>
+      <c r="E17" s="133" t="s">
+        <v>118</v>
       </c>
       <c r="F17" s="133" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="G17" s="133" t="s">
-        <v>290</v>
+        <v>118</v>
       </c>
       <c r="M17" s="132"/>
       <c r="R17" s="122" t="s">
@@ -10091,16 +10019,16 @@
       </c>
       <c r="B18" s="133"/>
       <c r="C18" s="133"/>
-      <c r="D18" s="118"/>
+      <c r="D18" s="118" t="s">
+        <v>128</v>
+      </c>
       <c r="E18" s="118" t="s">
-        <v>291</v>
+        <v>81</v>
       </c>
       <c r="F18" s="133" t="s">
-        <v>292</v>
-      </c>
-      <c r="G18" s="133" t="s">
-        <v>132</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="G18" s="133"/>
       <c r="M18" s="130"/>
       <c r="R18" s="122" t="s">
         <v>125</v>
@@ -10114,13 +10042,13 @@
       <c r="C19" s="133"/>
       <c r="D19" s="133"/>
       <c r="E19" s="118" t="s">
-        <v>293</v>
-      </c>
-      <c r="F19" s="133" t="s">
-        <v>132</v>
+        <v>279</v>
+      </c>
+      <c r="F19" s="118" t="s">
+        <v>81</v>
       </c>
       <c r="G19" s="133" t="s">
-        <v>292</v>
+        <v>124</v>
       </c>
       <c r="M19" s="130"/>
       <c r="R19" s="122" t="s">
@@ -10135,13 +10063,13 @@
       <c r="C20" s="118"/>
       <c r="D20" s="118"/>
       <c r="E20" s="118" t="s">
-        <v>277</v>
+        <v>123</v>
       </c>
       <c r="F20" s="133" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G20" s="133" t="s">
-        <v>294</v>
+        <v>263</v>
       </c>
       <c r="M20" s="132"/>
       <c r="R20" s="122" t="s">
@@ -10155,14 +10083,14 @@
       <c r="B21" s="118"/>
       <c r="C21" s="118"/>
       <c r="D21" s="118"/>
-      <c r="E21" s="118" t="s">
-        <v>295</v>
-      </c>
-      <c r="F21" s="133" t="s">
-        <v>294</v>
+      <c r="E21" s="133" t="s">
+        <v>263</v>
+      </c>
+      <c r="F21" s="118" t="s">
+        <v>123</v>
       </c>
       <c r="G21" s="133" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M21" s="132"/>
       <c r="R21" s="122" t="s">
@@ -10177,13 +10105,13 @@
       <c r="C22" s="133"/>
       <c r="D22" s="133"/>
       <c r="E22" s="118" t="s">
-        <v>296</v>
+        <v>136</v>
       </c>
       <c r="F22" s="133" t="s">
-        <v>87</v>
-      </c>
-      <c r="G22" s="133" t="s">
-        <v>249</v>
+        <v>263</v>
+      </c>
+      <c r="G22" s="118" t="s">
+        <v>123</v>
       </c>
       <c r="M22" s="130"/>
       <c r="R22" s="122" t="s">
@@ -10198,13 +10126,13 @@
       <c r="C23" s="133"/>
       <c r="D23" s="118"/>
       <c r="E23" s="118" t="s">
-        <v>297</v>
+        <v>108</v>
       </c>
       <c r="F23" s="133" t="s">
-        <v>249</v>
+        <v>96</v>
       </c>
       <c r="G23" s="133" t="s">
-        <v>96</v>
+        <v>280</v>
       </c>
       <c r="M23" s="132"/>
       <c r="R23" s="122" t="s">
@@ -10219,13 +10147,13 @@
       <c r="C24" s="133"/>
       <c r="D24" s="118"/>
       <c r="E24" s="118" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="F24" s="133" t="s">
-        <v>131</v>
+        <v>280</v>
       </c>
       <c r="G24" s="133" t="s">
-        <v>190</v>
+        <v>282</v>
       </c>
       <c r="M24" s="130"/>
       <c r="R24" s="122" t="s">
@@ -10236,17 +10164,17 @@
       <c r="A25" s="117" t="s">
         <v>148</v>
       </c>
-      <c r="B25" s="118" t="s">
-        <v>299</v>
-      </c>
-      <c r="C25" s="133" t="s">
-        <v>300</v>
-      </c>
+      <c r="B25" s="118"/>
+      <c r="C25" s="133"/>
       <c r="D25" s="133" t="s">
-        <v>143</v>
-      </c>
-      <c r="E25" s="118"/>
-      <c r="F25" s="133"/>
+        <v>108</v>
+      </c>
+      <c r="E25" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="F25" s="133" t="s">
+        <v>282</v>
+      </c>
       <c r="G25" s="133"/>
       <c r="M25" s="130"/>
       <c r="R25" s="122" t="s">
@@ -10257,17 +10185,17 @@
       <c r="A26" s="117" t="s">
         <v>152</v>
       </c>
-      <c r="B26" s="124" t="s">
-        <v>301</v>
-      </c>
-      <c r="C26" s="133" t="s">
-        <v>143</v>
-      </c>
+      <c r="B26" s="124"/>
+      <c r="C26" s="133"/>
       <c r="D26" s="133" t="s">
-        <v>300</v>
-      </c>
-      <c r="E26" s="124"/>
-      <c r="F26" s="133"/>
+        <v>123</v>
+      </c>
+      <c r="E26" s="133" t="s">
+        <v>282</v>
+      </c>
+      <c r="F26" s="133" t="s">
+        <v>283</v>
+      </c>
       <c r="G26" s="133"/>
       <c r="M26" s="132"/>
       <c r="R26" s="122" t="s">
@@ -10282,13 +10210,13 @@
       <c r="C27" s="131"/>
       <c r="D27" s="131"/>
       <c r="E27" s="124" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F27" s="133" t="s">
-        <v>302</v>
+        <v>118</v>
       </c>
       <c r="G27" s="133" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="M27" s="132"/>
       <c r="R27" s="122" t="s">
@@ -10303,10 +10231,10 @@
       <c r="C28" s="131"/>
       <c r="D28" s="131"/>
       <c r="E28" s="124" t="s">
-        <v>303</v>
+        <v>96</v>
       </c>
       <c r="F28" s="133" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="G28" s="131" t="s">
         <v>158</v>
@@ -10322,16 +10250,16 @@
       </c>
       <c r="B29" s="124"/>
       <c r="C29" s="131"/>
-      <c r="D29" s="131"/>
+      <c r="D29" s="124" t="s">
+        <v>284</v>
+      </c>
       <c r="E29" s="124" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="F29" s="124" t="s">
-        <v>305</v>
-      </c>
-      <c r="G29" s="124" t="s">
-        <v>306</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="G29" s="124"/>
       <c r="M29" s="130"/>
       <c r="R29" s="122" t="s">
         <v>123</v>
@@ -10345,13 +10273,13 @@
       <c r="C30" s="131"/>
       <c r="D30" s="131"/>
       <c r="E30" s="124" t="s">
-        <v>307</v>
+        <v>167</v>
       </c>
       <c r="F30" s="124" t="s">
-        <v>306</v>
+        <v>285</v>
       </c>
       <c r="G30" s="124" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="M30" s="132"/>
       <c r="R30" s="122" t="s">
@@ -10366,13 +10294,13 @@
       <c r="C31" s="131"/>
       <c r="D31" s="131"/>
       <c r="E31" s="124" t="s">
-        <v>308</v>
+        <v>208</v>
       </c>
       <c r="F31" s="131" t="s">
-        <v>309</v>
-      </c>
-      <c r="G31" s="131" t="s">
-        <v>310</v>
+        <v>169</v>
+      </c>
+      <c r="G31" s="124" t="s">
+        <v>208</v>
       </c>
       <c r="M31" s="130"/>
       <c r="R31" s="122" t="s">
@@ -10386,15 +10314,13 @@
       <c r="B32" s="124"/>
       <c r="C32" s="131"/>
       <c r="D32" s="131"/>
-      <c r="E32" s="124" t="s">
-        <v>279</v>
+      <c r="E32" s="131" t="s">
+        <v>169</v>
       </c>
       <c r="F32" s="131" t="s">
-        <v>310</v>
-      </c>
-      <c r="G32" s="131" t="s">
-        <v>309</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="G32" s="131"/>
       <c r="M32" s="130"/>
       <c r="R32" s="122" t="s">
         <v>173</v>
@@ -10407,14 +10333,14 @@
       <c r="B33" s="124"/>
       <c r="C33" s="131"/>
       <c r="D33" s="131"/>
-      <c r="E33" s="124" t="s">
-        <v>281</v>
-      </c>
-      <c r="F33" s="131" t="s">
-        <v>311</v>
+      <c r="E33" s="131" t="s">
+        <v>287</v>
+      </c>
+      <c r="F33" s="124" t="s">
+        <v>208</v>
       </c>
       <c r="G33" s="131" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="M33" s="132"/>
       <c r="R33" s="122" t="s">
@@ -10429,14 +10355,12 @@
       <c r="C34" s="131"/>
       <c r="D34" s="131"/>
       <c r="E34" s="118" t="s">
-        <v>282</v>
-      </c>
-      <c r="F34" s="134" t="s">
         <v>220</v>
       </c>
-      <c r="G34" s="134" t="s">
+      <c r="F34" s="118" t="s">
         <v>220</v>
       </c>
+      <c r="G34" s="134"/>
       <c r="M34" s="129"/>
       <c r="R34" s="122" t="s">
         <v>179</v>
@@ -10448,16 +10372,16 @@
       </c>
       <c r="B35" s="124"/>
       <c r="C35" s="131"/>
-      <c r="D35" s="131"/>
-      <c r="E35" s="118" t="s">
-        <v>287</v>
+      <c r="D35" s="131" t="s">
+        <v>289</v>
+      </c>
+      <c r="E35" s="131" t="s">
+        <v>289</v>
       </c>
       <c r="F35" s="134" t="s">
-        <v>312</v>
-      </c>
-      <c r="G35" s="131" t="s">
-        <v>311</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="G35" s="131"/>
       <c r="M35" s="129"/>
       <c r="R35" s="122" t="s">
         <v>182</v>
@@ -10468,13 +10392,13 @@
         <v>183</v>
       </c>
       <c r="B36" s="118" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="C36" s="131" t="s">
-        <v>313</v>
+        <v>292</v>
       </c>
       <c r="D36" s="131" t="s">
-        <v>214</v>
+        <v>293</v>
       </c>
       <c r="E36" s="136"/>
       <c r="F36" s="137"/>
@@ -10488,16 +10412,14 @@
       <c r="A37" s="117" t="s">
         <v>188</v>
       </c>
-      <c r="B37" s="118" t="s">
-        <v>314</v>
-      </c>
-      <c r="C37" s="131" t="s">
-        <v>186</v>
-      </c>
+      <c r="B37" s="118"/>
+      <c r="C37" s="131"/>
       <c r="D37" s="131" t="s">
-        <v>313</v>
-      </c>
-      <c r="E37" s="127"/>
+        <v>237</v>
+      </c>
+      <c r="E37" s="131" t="s">
+        <v>291</v>
+      </c>
       <c r="F37" s="131"/>
       <c r="G37" s="131"/>
       <c r="M37" s="145"/>
@@ -10509,11 +10431,11 @@
       <c r="A38" s="117" t="s">
         <v>191</v>
       </c>
-      <c r="B38" s="118" t="s">
-        <v>315</v>
+      <c r="B38" s="131" t="s">
+        <v>237</v>
       </c>
       <c r="C38" s="131" t="s">
-        <v>214</v>
+        <v>293</v>
       </c>
       <c r="D38" s="131" t="s">
         <v>186</v>
@@ -10531,10 +10453,10 @@
         <v>193</v>
       </c>
       <c r="B39" s="118" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="C39" s="131" t="s">
-        <v>316</v>
+        <v>294</v>
       </c>
       <c r="D39" s="131" t="s">
         <v>217</v>
@@ -10551,14 +10473,14 @@
       <c r="A40" s="117" t="s">
         <v>196</v>
       </c>
-      <c r="B40" s="118" t="s">
-        <v>296</v>
+      <c r="B40" s="131" t="s">
+        <v>217</v>
       </c>
       <c r="C40" s="131" t="s">
         <v>217</v>
       </c>
-      <c r="D40" s="131" t="s">
-        <v>316</v>
+      <c r="D40" s="118" t="s">
+        <v>287</v>
       </c>
       <c r="E40" s="127"/>
       <c r="F40" s="134"/>
@@ -10573,16 +10495,16 @@
       <c r="A41" s="135" t="s">
         <v>197</v>
       </c>
-      <c r="B41" s="118" t="s">
-        <v>284</v>
-      </c>
+      <c r="B41" s="131"/>
       <c r="C41" s="131" t="s">
         <v>198</v>
       </c>
       <c r="D41" s="131" t="s">
         <v>198</v>
       </c>
-      <c r="E41" s="140"/>
+      <c r="E41" s="131" t="s">
+        <v>294</v>
+      </c>
       <c r="F41" s="141"/>
       <c r="G41" s="141"/>
       <c r="J41" s="146"/>
@@ -11509,13 +11431,13 @@
     <dataValidation type="list" allowBlank="1" sqref="E37:E38 E40">
       <formula1>'ПЯТНИЦА'!$O$3:$O$130</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B3:E4 B5:G13 B14:D14 F14:G14 B15:G17 D18:G18 B19 E19:G19 B20:G26 E27:G27 E28:F28 E29:G30 E31:E32 E33:G33 C29:C35 E34:E35 G35 B36:C36 B37:D37 B38 D38 B39:G39 B40:D40 B41:E41 B42:C42">
+    <dataValidation type="list" allowBlank="1" sqref="B3:E4 B5:G13 B14:D14 F14:G14 B15:G17 B19 D18:G19 B20:G26 E27:G27 E28:F28 C29:G29 E30:G30 E31 G31 F33:G33 E34:F34 C30:C35 G35 B36:C36 B37:D37 B38 D38 B39:G39 B40:D40 B41:E41 B42:C42">
       <formula1>'СУББОТА'!$O$3:$O$130</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B18:C18 C19:D19 F37:G38">
+    <dataValidation type="list" allowBlank="1" sqref="B18:C18 C19 F37:G38">
       <formula1>'ВТОРНИК'!$P$3:$P$130</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F3:G4 E14 B27:D28 G28 F31:G32 F34:G34 B29:B35 D29:D35 F35 D36:G36 C38 F40:G41 D42:G42">
+    <dataValidation type="list" allowBlank="1" sqref="F3:G4 E14 B27:D28 G28 D30:D31 F31 D32:G32 D33:E33 D34 G34 B29:B35 D35:F35 D36:G36 C38 F40:G41 D42:G42">
       <formula1>'ПОНЕДЕЛЬНИК'!$O$3:$O$130</formula1>
     </dataValidation>
   </dataValidations>
@@ -11603,10 +11525,10 @@
     </row>
     <row r="4" ht="26.25" customHeight="1">
       <c r="A4" s="117" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="B4" s="118" t="s">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="C4" s="118" t="s">
         <v>77</v>
@@ -11686,7 +11608,7 @@
         <v>92</v>
       </c>
       <c r="B8" s="118" t="s">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="C8" s="118" t="s">
         <v>90</v>
@@ -11801,7 +11723,7 @@
         <v>83</v>
       </c>
       <c r="D12" s="118" t="s">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="E12" s="118"/>
       <c r="F12" s="118"/>
@@ -11822,7 +11744,7 @@
         <v>244</v>
       </c>
       <c r="D13" s="118" t="s">
-        <v>320</v>
+        <v>275</v>
       </c>
       <c r="E13" s="118"/>
       <c r="F13" s="118"/>
@@ -11902,13 +11824,13 @@
       <c r="B17" s="133"/>
       <c r="C17" s="133"/>
       <c r="D17" s="118" t="s">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="E17" s="118" t="s">
         <v>118</v>
       </c>
       <c r="F17" s="118" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G17" s="133"/>
       <c r="K17" s="132"/>
@@ -11948,7 +11870,7 @@
         <v>108</v>
       </c>
       <c r="F19" s="118" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="G19" s="133" t="s">
         <v>167</v>
@@ -11969,7 +11891,7 @@
         <v>87</v>
       </c>
       <c r="F20" s="133" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="G20" s="118" t="s">
         <v>136</v>
@@ -11987,13 +11909,13 @@
       <c r="C21" s="118"/>
       <c r="D21" s="118"/>
       <c r="E21" s="118" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="F21" s="118" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
       <c r="G21" s="133" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="K21" s="132"/>
       <c r="O21" s="122" t="s">
@@ -12008,13 +11930,13 @@
       <c r="C22" s="133"/>
       <c r="D22" s="133"/>
       <c r="E22" s="133" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="F22" s="118" t="s">
         <v>87</v>
       </c>
       <c r="G22" s="118" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
       <c r="K22" s="130"/>
       <c r="O22" s="122" t="s">
@@ -12032,7 +11954,7 @@
         <v>96</v>
       </c>
       <c r="F23" s="133" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="G23" s="133"/>
       <c r="K23" s="132"/>
@@ -12054,7 +11976,7 @@
         <v>108</v>
       </c>
       <c r="G24" s="133" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="K24" s="130"/>
       <c r="O24" s="122" t="s">
@@ -12109,13 +12031,13 @@
       <c r="C27" s="131"/>
       <c r="D27" s="131"/>
       <c r="E27" s="124" t="s">
-        <v>326</v>
+        <v>278</v>
       </c>
       <c r="F27" s="133" t="s">
         <v>118</v>
       </c>
       <c r="G27" s="133" t="s">
-        <v>327</v>
+        <v>305</v>
       </c>
       <c r="K27" s="132"/>
       <c r="O27" s="122" t="s">
@@ -12154,10 +12076,10 @@
         <v>167</v>
       </c>
       <c r="F29" s="124" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="G29" s="124" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K29" s="130"/>
       <c r="O29" s="122" t="s">
@@ -12172,13 +12094,13 @@
       <c r="C30" s="131"/>
       <c r="D30" s="131"/>
       <c r="E30" s="124" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F30" s="124" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G30" s="124" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="K30" s="132"/>
       <c r="O30" s="122" t="s">
@@ -12193,13 +12115,13 @@
       <c r="C31" s="131"/>
       <c r="D31" s="131"/>
       <c r="E31" s="124" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="F31" s="131" t="s">
         <v>169</v>
       </c>
       <c r="G31" s="131" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
       <c r="K31" s="130"/>
       <c r="O31" s="122" t="s">
@@ -12217,7 +12139,7 @@
         <v>208</v>
       </c>
       <c r="F32" s="124" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="G32" s="131" t="s">
         <v>169</v>
@@ -12238,10 +12160,10 @@
         <v>258</v>
       </c>
       <c r="F33" s="124" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="G33" s="124" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="K33" s="132"/>
       <c r="O33" s="122" t="s">
@@ -12277,13 +12199,13 @@
       <c r="C35" s="131"/>
       <c r="D35" s="131"/>
       <c r="E35" s="118" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F35" s="118" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G35" s="118" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K35" s="129"/>
       <c r="O35" s="122" t="s">
@@ -12295,7 +12217,7 @@
         <v>183</v>
       </c>
       <c r="B36" s="118" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C36" s="131" t="s">
         <v>214</v>
@@ -12316,10 +12238,10 @@
         <v>188</v>
       </c>
       <c r="B37" s="118" t="s">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="C37" s="118" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="D37" s="131" t="s">
         <v>214</v>
@@ -12340,10 +12262,10 @@
         <v>214</v>
       </c>
       <c r="C38" s="131" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="D38" s="118" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="E38" s="127"/>
       <c r="F38" s="131"/>
@@ -12364,7 +12286,7 @@
         <v>217</v>
       </c>
       <c r="D39" s="124" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="E39" s="131"/>
       <c r="F39" s="131"/>
@@ -12382,7 +12304,7 @@
         <v>132</v>
       </c>
       <c r="C40" s="124" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="D40" s="118" t="s">
         <v>217</v>
@@ -13286,7 +13208,7 @@
         <v>70</v>
       </c>
       <c r="B1" s="154" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="D1" s="155">
         <v>46268.0</v>
@@ -13340,13 +13262,13 @@
     </row>
     <row r="4" ht="26.25" customHeight="1">
       <c r="A4" s="117" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="B4" s="118" t="s">
         <v>246</v>
       </c>
       <c r="C4" s="118" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="D4" s="118" t="s">
         <v>76</v>
@@ -13423,7 +13345,7 @@
         <v>92</v>
       </c>
       <c r="B8" s="118" t="s">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="C8" s="118" t="s">
         <v>84</v>
@@ -13510,10 +13432,10 @@
         <v>76</v>
       </c>
       <c r="C12" s="118" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="D12" s="118" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="E12" s="118"/>
       <c r="F12" s="118"/>
@@ -13528,7 +13450,7 @@
         <v>106</v>
       </c>
       <c r="B13" s="118" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="C13" s="118" t="s">
         <v>76</v>
@@ -13619,7 +13541,7 @@
         <v>118</v>
       </c>
       <c r="E17" s="118" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F17" s="133"/>
       <c r="G17" s="133"/>
@@ -13638,10 +13560,10 @@
         <v>249</v>
       </c>
       <c r="E18" s="118" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="F18" s="118" t="s">
-        <v>339</v>
+        <v>282</v>
       </c>
       <c r="G18" s="133"/>
       <c r="I18" s="158" t="s">
@@ -13666,7 +13588,7 @@
         <v>124</v>
       </c>
       <c r="G19" s="118" t="s">
-        <v>339</v>
+        <v>282</v>
       </c>
       <c r="L19" s="132"/>
       <c r="O19" s="122" t="s">
@@ -13723,7 +13645,7 @@
       <c r="C22" s="133"/>
       <c r="D22" s="133"/>
       <c r="E22" s="118" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="F22" s="133" t="s">
         <v>263</v>
@@ -13747,7 +13669,7 @@
         <v>93</v>
       </c>
       <c r="F23" s="118" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
       <c r="G23" s="133"/>
       <c r="L23" s="130"/>
@@ -13830,7 +13752,7 @@
         <v>77</v>
       </c>
       <c r="G27" s="133" t="s">
-        <v>326</v>
+        <v>278</v>
       </c>
       <c r="L27" s="132"/>
       <c r="O27" s="122" t="s">
@@ -13866,13 +13788,13 @@
       <c r="C29" s="131"/>
       <c r="D29" s="131"/>
       <c r="E29" s="124" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F29" s="124" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G29" s="124" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="L29" s="132"/>
       <c r="O29" s="122" t="s">
@@ -13887,13 +13809,13 @@
       <c r="C30" s="131"/>
       <c r="D30" s="131"/>
       <c r="E30" s="124" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="F30" s="124" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="G30" s="124" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L30" s="130"/>
       <c r="O30" s="122" t="s">
@@ -13931,7 +13853,7 @@
         <v>167</v>
       </c>
       <c r="E32" s="124" t="s">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="F32" s="124" t="s">
         <v>132</v>
@@ -14013,7 +13935,7 @@
         <v>214</v>
       </c>
       <c r="C36" s="131" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="D36" s="118" t="s">
         <v>173</v>
@@ -14037,7 +13959,7 @@
         <v>214</v>
       </c>
       <c r="D37" s="131" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="E37" s="127"/>
       <c r="F37" s="131"/>
@@ -14072,7 +13994,7 @@
       </c>
       <c r="B39" s="118"/>
       <c r="C39" s="131" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="D39" s="131" t="s">
         <v>217</v>
@@ -14098,7 +14020,7 @@
         <v>217</v>
       </c>
       <c r="D40" s="131" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="E40" s="127"/>
       <c r="F40" s="134"/>
@@ -15041,7 +14963,7 @@
         <v>204</v>
       </c>
       <c r="C3" s="118" t="s">
-        <v>343</v>
+        <v>323</v>
       </c>
       <c r="D3" s="118" t="s">
         <v>88</v>
@@ -15057,16 +14979,16 @@
     </row>
     <row r="4" ht="26.25" customHeight="1">
       <c r="A4" s="117" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="B4" s="118" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="C4" s="118" t="s">
         <v>90</v>
       </c>
       <c r="D4" s="118" t="s">
-        <v>343</v>
+        <v>323</v>
       </c>
       <c r="E4" s="118"/>
       <c r="F4" s="119"/>
@@ -15110,7 +15032,7 @@
         <v>182</v>
       </c>
       <c r="D6" s="118" t="s">
-        <v>346</v>
+        <v>273</v>
       </c>
       <c r="E6" s="118"/>
       <c r="F6" s="118"/>
@@ -15124,10 +15046,10 @@
         <v>89</v>
       </c>
       <c r="B7" s="118" t="s">
-        <v>346</v>
+        <v>273</v>
       </c>
       <c r="C7" s="118" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="D7" s="118" t="s">
         <v>182</v>
@@ -15150,7 +15072,7 @@
         <v>77</v>
       </c>
       <c r="D8" s="118" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="E8" s="118"/>
       <c r="F8" s="118"/>
@@ -15167,7 +15089,7 @@
         <v>96</v>
       </c>
       <c r="C9" s="118" t="s">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="D9" s="118" t="s">
         <v>83</v>
@@ -15212,7 +15134,7 @@
         <v>93</v>
       </c>
       <c r="D11" s="118" t="s">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="E11" s="118"/>
       <c r="F11" s="118"/>
@@ -15404,7 +15326,7 @@
         <v>133</v>
       </c>
       <c r="G20" s="133" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="L20" s="132"/>
       <c r="O20" s="122" t="s">
@@ -15419,7 +15341,7 @@
       <c r="C21" s="118"/>
       <c r="D21" s="118"/>
       <c r="E21" s="133" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="F21" s="133" t="s">
         <v>87</v>
@@ -15443,7 +15365,7 @@
         <v>133</v>
       </c>
       <c r="F22" s="133" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="G22" s="133" t="s">
         <v>87</v>
@@ -15460,13 +15382,13 @@
       <c r="B23" s="133"/>
       <c r="C23" s="133"/>
       <c r="D23" s="118" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="E23" s="118" t="s">
         <v>96</v>
       </c>
       <c r="F23" s="118" t="s">
-        <v>350</v>
+        <v>280</v>
       </c>
       <c r="G23" s="133"/>
       <c r="L23" s="132"/>
@@ -15503,13 +15425,13 @@
       <c r="C25" s="133"/>
       <c r="D25" s="133"/>
       <c r="E25" s="118" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="F25" s="118" t="s">
         <v>96</v>
       </c>
       <c r="G25" s="118" t="s">
-        <v>350</v>
+        <v>280</v>
       </c>
       <c r="L25" s="130"/>
       <c r="O25" s="122" t="s">
@@ -15570,7 +15492,7 @@
         <v>159</v>
       </c>
       <c r="G28" s="124" t="s">
-        <v>327</v>
+        <v>305</v>
       </c>
       <c r="L28" s="132"/>
       <c r="O28" s="122" t="s">
@@ -15591,7 +15513,7 @@
         <v>167</v>
       </c>
       <c r="G29" s="124" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L29" s="130"/>
       <c r="O29" s="122" t="s">
@@ -15606,10 +15528,10 @@
       <c r="C30" s="131"/>
       <c r="D30" s="131"/>
       <c r="E30" s="124" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F30" s="124" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G30" s="124" t="s">
         <v>167</v>
@@ -15709,7 +15631,7 @@
       </c>
       <c r="B35" s="124"/>
       <c r="C35" s="131" t="s">
-        <v>351</v>
+        <v>329</v>
       </c>
       <c r="D35" s="131" t="s">
         <v>235</v>
@@ -15736,7 +15658,7 @@
         <v>184</v>
       </c>
       <c r="E36" s="136" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="F36" s="137"/>
       <c r="G36" s="137"/>
@@ -15756,7 +15678,7 @@
         <v>184</v>
       </c>
       <c r="F37" s="136" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="G37" s="131"/>
       <c r="L37" s="145"/>
@@ -15772,13 +15694,13 @@
       <c r="C38" s="118"/>
       <c r="D38" s="118"/>
       <c r="E38" s="118" t="s">
-        <v>353</v>
+        <v>331</v>
       </c>
       <c r="F38" s="131" t="s">
         <v>132</v>
       </c>
       <c r="G38" s="136" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="L38" s="132"/>
       <c r="O38" s="122" t="s">
@@ -15793,10 +15715,10 @@
         <v>217</v>
       </c>
       <c r="C39" s="118" t="s">
-        <v>354</v>
+        <v>332</v>
       </c>
       <c r="D39" s="118" t="s">
-        <v>354</v>
+        <v>332</v>
       </c>
       <c r="E39" s="131"/>
       <c r="F39" s="131"/>
@@ -17147,16 +17069,16 @@
       <c r="B1" s="149" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="165">
-        <v>46270.0</v>
+      <c r="D1" s="150">
+        <v>46179.0</v>
       </c>
       <c r="E1" s="151"/>
       <c r="F1" s="152"/>
       <c r="G1" s="152"/>
-      <c r="H1" s="166"/>
-      <c r="I1" s="166"/>
-      <c r="J1" s="166"/>
-      <c r="K1" s="166"/>
+      <c r="H1" s="165"/>
+      <c r="I1" s="165"/>
+      <c r="J1" s="165"/>
+      <c r="K1" s="165"/>
     </row>
     <row r="2">
       <c r="A2" s="116" t="s">
@@ -17180,10 +17102,10 @@
       <c r="G2" s="116" t="s">
         <v>73</v>
       </c>
-      <c r="H2" s="166"/>
-      <c r="I2" s="166"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="166"/>
+      <c r="H2" s="165"/>
+      <c r="I2" s="165"/>
+      <c r="J2" s="165"/>
+      <c r="K2" s="165"/>
     </row>
     <row r="3" ht="26.25" customHeight="1">
       <c r="A3" s="117" t="s">
@@ -17199,17 +17121,17 @@
       <c r="E3" s="118"/>
       <c r="F3" s="119"/>
       <c r="G3" s="120"/>
-      <c r="H3" s="166"/>
-      <c r="I3" s="166"/>
-      <c r="J3" s="166"/>
-      <c r="K3" s="166"/>
+      <c r="H3" s="165"/>
+      <c r="I3" s="165"/>
+      <c r="J3" s="165"/>
+      <c r="K3" s="165"/>
       <c r="O3" s="122" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="4" ht="27.0" customHeight="1">
       <c r="A4" s="117" t="s">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="B4" s="118" t="s">
         <v>246</v>
@@ -17223,10 +17145,10 @@
       <c r="E4" s="118"/>
       <c r="F4" s="119"/>
       <c r="G4" s="120"/>
-      <c r="H4" s="166"/>
-      <c r="I4" s="166"/>
-      <c r="J4" s="166"/>
-      <c r="K4" s="166"/>
+      <c r="H4" s="165"/>
+      <c r="I4" s="165"/>
+      <c r="J4" s="165"/>
+      <c r="K4" s="165"/>
       <c r="O4" s="122" t="s">
         <v>81</v>
       </c>
@@ -17245,10 +17167,10 @@
       <c r="E5" s="118"/>
       <c r="F5" s="118"/>
       <c r="G5" s="124"/>
-      <c r="H5" s="166"/>
-      <c r="I5" s="166"/>
-      <c r="J5" s="166"/>
-      <c r="K5" s="166"/>
+      <c r="H5" s="165"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="165"/>
+      <c r="K5" s="165"/>
       <c r="O5" s="122" t="s">
         <v>83</v>
       </c>
@@ -17269,10 +17191,10 @@
       <c r="E6" s="118"/>
       <c r="F6" s="118"/>
       <c r="G6" s="124"/>
-      <c r="H6" s="166"/>
-      <c r="I6" s="166"/>
-      <c r="J6" s="166"/>
-      <c r="K6" s="166"/>
+      <c r="H6" s="165"/>
+      <c r="I6" s="165"/>
+      <c r="J6" s="165"/>
+      <c r="K6" s="165"/>
       <c r="O6" s="122" t="s">
         <v>88</v>
       </c>
@@ -17291,10 +17213,10 @@
       <c r="E7" s="118"/>
       <c r="F7" s="118"/>
       <c r="G7" s="124"/>
-      <c r="H7" s="166"/>
-      <c r="I7" s="166"/>
-      <c r="J7" s="166"/>
-      <c r="K7" s="166"/>
+      <c r="H7" s="165"/>
+      <c r="I7" s="165"/>
+      <c r="J7" s="165"/>
+      <c r="K7" s="165"/>
       <c r="O7" s="122" t="s">
         <v>91</v>
       </c>
@@ -17311,14 +17233,14 @@
         <v>83</v>
       </c>
       <c r="E8" s="118" t="s">
-        <v>356</v>
+        <v>334</v>
       </c>
       <c r="F8" s="118"/>
       <c r="G8" s="124"/>
-      <c r="H8" s="166"/>
-      <c r="I8" s="166"/>
-      <c r="J8" s="166"/>
-      <c r="K8" s="166"/>
+      <c r="H8" s="165"/>
+      <c r="I8" s="165"/>
+      <c r="J8" s="165"/>
+      <c r="K8" s="165"/>
       <c r="O8" s="122" t="s">
         <v>90</v>
       </c>
@@ -17339,10 +17261,10 @@
       <c r="E9" s="118"/>
       <c r="F9" s="118"/>
       <c r="G9" s="124"/>
-      <c r="H9" s="166"/>
-      <c r="I9" s="166"/>
-      <c r="J9" s="166"/>
-      <c r="K9" s="166"/>
+      <c r="H9" s="165"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="165"/>
       <c r="L9" s="126"/>
       <c r="O9" s="122" t="s">
         <v>98</v>
@@ -17360,14 +17282,14 @@
       </c>
       <c r="D10" s="118"/>
       <c r="E10" s="118" t="s">
-        <v>356</v>
+        <v>334</v>
       </c>
       <c r="F10" s="127"/>
       <c r="G10" s="128"/>
-      <c r="H10" s="166"/>
-      <c r="I10" s="166"/>
-      <c r="J10" s="166"/>
-      <c r="K10" s="166"/>
+      <c r="H10" s="165"/>
+      <c r="I10" s="165"/>
+      <c r="J10" s="165"/>
+      <c r="K10" s="165"/>
       <c r="L10" s="129"/>
       <c r="O10" s="122" t="s">
         <v>100</v>
@@ -17382,15 +17304,15 @@
         <v>97</v>
       </c>
       <c r="D11" s="118" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="E11" s="118"/>
       <c r="F11" s="118"/>
       <c r="G11" s="124"/>
-      <c r="H11" s="166"/>
-      <c r="I11" s="166"/>
-      <c r="J11" s="166"/>
-      <c r="K11" s="166"/>
+      <c r="H11" s="165"/>
+      <c r="I11" s="165"/>
+      <c r="J11" s="165"/>
+      <c r="K11" s="165"/>
       <c r="L11" s="129"/>
       <c r="O11" s="122" t="s">
         <v>102</v>
@@ -17404,7 +17326,7 @@
         <v>97</v>
       </c>
       <c r="C12" s="118" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="D12" s="118" t="s">
         <v>204</v>
@@ -17412,10 +17334,10 @@
       <c r="E12" s="118"/>
       <c r="F12" s="118"/>
       <c r="G12" s="124"/>
-      <c r="H12" s="166"/>
-      <c r="I12" s="166"/>
-      <c r="J12" s="166"/>
-      <c r="K12" s="166"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="165"/>
+      <c r="J12" s="165"/>
+      <c r="K12" s="165"/>
       <c r="L12" s="130"/>
       <c r="O12" s="122" t="s">
         <v>105</v>
@@ -17426,21 +17348,21 @@
         <v>106</v>
       </c>
       <c r="B13" s="118" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="C13" s="118" t="s">
         <v>88</v>
       </c>
       <c r="D13" s="118" t="s">
-        <v>320</v>
+        <v>275</v>
       </c>
       <c r="E13" s="118"/>
       <c r="F13" s="118"/>
       <c r="G13" s="124"/>
-      <c r="H13" s="166"/>
-      <c r="I13" s="166"/>
-      <c r="J13" s="166"/>
-      <c r="K13" s="166"/>
+      <c r="H13" s="165"/>
+      <c r="I13" s="165"/>
+      <c r="J13" s="165"/>
+      <c r="K13" s="165"/>
       <c r="L13" s="130"/>
       <c r="O13" s="122" t="s">
         <v>108</v>
@@ -17454,7 +17376,7 @@
         <v>96</v>
       </c>
       <c r="C14" s="118" t="s">
-        <v>320</v>
+        <v>275</v>
       </c>
       <c r="D14" s="118" t="s">
         <v>88</v>
@@ -17462,10 +17384,10 @@
       <c r="E14" s="131"/>
       <c r="F14" s="118"/>
       <c r="G14" s="124"/>
-      <c r="H14" s="166"/>
-      <c r="I14" s="166"/>
-      <c r="J14" s="166"/>
-      <c r="K14" s="166"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="165"/>
+      <c r="J14" s="165"/>
+      <c r="K14" s="165"/>
       <c r="L14" s="130"/>
       <c r="O14" s="122" t="s">
         <v>111</v>
@@ -17476,21 +17398,21 @@
         <v>112</v>
       </c>
       <c r="B15" s="118" t="s">
-        <v>358</v>
+        <v>281</v>
       </c>
       <c r="C15" s="118" t="s">
         <v>255</v>
       </c>
       <c r="D15" s="118"/>
       <c r="E15" s="118" t="s">
-        <v>356</v>
+        <v>334</v>
       </c>
       <c r="F15" s="118"/>
       <c r="G15" s="124"/>
-      <c r="H15" s="166"/>
-      <c r="I15" s="166"/>
-      <c r="J15" s="166"/>
-      <c r="K15" s="166"/>
+      <c r="H15" s="165"/>
+      <c r="I15" s="165"/>
+      <c r="J15" s="165"/>
+      <c r="K15" s="165"/>
       <c r="L15" s="130"/>
       <c r="O15" s="122" t="s">
         <v>114</v>
@@ -17512,10 +17434,10 @@
       <c r="E16" s="118"/>
       <c r="F16" s="133"/>
       <c r="G16" s="131"/>
-      <c r="H16" s="166"/>
-      <c r="I16" s="166"/>
-      <c r="J16" s="166"/>
-      <c r="K16" s="166"/>
+      <c r="H16" s="165"/>
+      <c r="I16" s="165"/>
+      <c r="J16" s="165"/>
+      <c r="K16" s="165"/>
       <c r="L16" s="130"/>
       <c r="O16" s="122" t="s">
         <v>116</v>
@@ -17526,7 +17448,7 @@
         <v>117</v>
       </c>
       <c r="B17" s="133" t="s">
-        <v>326</v>
+        <v>278</v>
       </c>
       <c r="C17" s="133" t="s">
         <v>118</v>
@@ -17535,10 +17457,10 @@
       <c r="E17" s="118"/>
       <c r="F17" s="133"/>
       <c r="G17" s="133"/>
-      <c r="H17" s="166"/>
-      <c r="I17" s="166"/>
-      <c r="J17" s="166"/>
-      <c r="K17" s="166"/>
+      <c r="H17" s="165"/>
+      <c r="I17" s="165"/>
+      <c r="J17" s="165"/>
+      <c r="K17" s="165"/>
       <c r="L17" s="130"/>
       <c r="O17" s="122" t="s">
         <v>120</v>
@@ -17558,10 +17480,10 @@
       </c>
       <c r="F18" s="133"/>
       <c r="G18" s="133"/>
-      <c r="H18" s="166"/>
-      <c r="I18" s="166"/>
-      <c r="J18" s="166"/>
-      <c r="K18" s="166"/>
+      <c r="H18" s="165"/>
+      <c r="I18" s="165"/>
+      <c r="J18" s="165"/>
+      <c r="K18" s="165"/>
       <c r="L18" s="130"/>
       <c r="O18" s="122" t="s">
         <v>125</v>
@@ -17572,7 +17494,7 @@
         <v>126</v>
       </c>
       <c r="B19" s="133" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="C19" s="133" t="s">
         <v>136</v>
@@ -17583,10 +17505,10 @@
       <c r="E19" s="118"/>
       <c r="F19" s="118"/>
       <c r="G19" s="118"/>
-      <c r="H19" s="166"/>
-      <c r="I19" s="166"/>
-      <c r="J19" s="166"/>
-      <c r="K19" s="166"/>
+      <c r="H19" s="165"/>
+      <c r="I19" s="165"/>
+      <c r="J19" s="165"/>
+      <c r="K19" s="165"/>
       <c r="L19" s="130"/>
       <c r="O19" s="122" t="s">
         <v>129</v>
@@ -17608,10 +17530,10 @@
       <c r="E20" s="133"/>
       <c r="F20" s="133"/>
       <c r="G20" s="133"/>
-      <c r="H20" s="166"/>
-      <c r="I20" s="166"/>
-      <c r="J20" s="166"/>
-      <c r="K20" s="166"/>
+      <c r="H20" s="165"/>
+      <c r="I20" s="165"/>
+      <c r="J20" s="165"/>
+      <c r="K20" s="165"/>
       <c r="L20" s="130"/>
       <c r="O20" s="122" t="s">
         <v>134</v>
@@ -17631,10 +17553,10 @@
       <c r="E21" s="133"/>
       <c r="F21" s="133"/>
       <c r="G21" s="133"/>
-      <c r="H21" s="166"/>
-      <c r="I21" s="166"/>
-      <c r="J21" s="166"/>
-      <c r="K21" s="166"/>
+      <c r="H21" s="165"/>
+      <c r="I21" s="165"/>
+      <c r="J21" s="165"/>
+      <c r="K21" s="165"/>
       <c r="L21" s="130"/>
       <c r="O21" s="122" t="s">
         <v>138</v>
@@ -17654,10 +17576,10 @@
       </c>
       <c r="F22" s="133"/>
       <c r="G22" s="133"/>
-      <c r="H22" s="166"/>
-      <c r="I22" s="166"/>
-      <c r="J22" s="166"/>
-      <c r="K22" s="166"/>
+      <c r="H22" s="165"/>
+      <c r="I22" s="165"/>
+      <c r="J22" s="165"/>
+      <c r="K22" s="165"/>
       <c r="L22" s="130"/>
       <c r="O22" s="122" t="s">
         <v>141</v>
@@ -17677,10 +17599,10 @@
       <c r="E23" s="118"/>
       <c r="F23" s="118"/>
       <c r="G23" s="133"/>
-      <c r="H23" s="166"/>
-      <c r="I23" s="166"/>
-      <c r="J23" s="166"/>
-      <c r="K23" s="166"/>
+      <c r="H23" s="165"/>
+      <c r="I23" s="165"/>
+      <c r="J23" s="165"/>
+      <c r="K23" s="165"/>
       <c r="L23" s="130"/>
       <c r="O23" s="122" t="s">
         <v>144</v>
@@ -17694,16 +17616,16 @@
         <v>179</v>
       </c>
       <c r="C24" s="133" t="s">
-        <v>350</v>
+        <v>280</v>
       </c>
       <c r="D24" s="133"/>
       <c r="E24" s="118"/>
       <c r="F24" s="118"/>
       <c r="G24" s="133"/>
-      <c r="H24" s="166"/>
-      <c r="I24" s="166"/>
-      <c r="J24" s="166"/>
-      <c r="K24" s="166"/>
+      <c r="H24" s="165"/>
+      <c r="I24" s="165"/>
+      <c r="J24" s="165"/>
+      <c r="K24" s="165"/>
       <c r="L24" s="130"/>
       <c r="O24" s="122" t="s">
         <v>147</v>
@@ -17720,15 +17642,15 @@
         <v>111</v>
       </c>
       <c r="D25" s="133" t="s">
-        <v>350</v>
+        <v>280</v>
       </c>
       <c r="E25" s="118"/>
       <c r="F25" s="118"/>
       <c r="G25" s="118"/>
-      <c r="H25" s="166"/>
-      <c r="I25" s="166"/>
-      <c r="J25" s="166"/>
-      <c r="K25" s="166"/>
+      <c r="H25" s="165"/>
+      <c r="I25" s="165"/>
+      <c r="J25" s="165"/>
+      <c r="K25" s="165"/>
       <c r="L25" s="130"/>
       <c r="O25" s="122" t="s">
         <v>151</v>
@@ -17746,14 +17668,14 @@
         <v>96</v>
       </c>
       <c r="E26" s="133" t="s">
-        <v>350</v>
+        <v>280</v>
       </c>
       <c r="F26" s="133"/>
       <c r="G26" s="118"/>
-      <c r="H26" s="166"/>
-      <c r="I26" s="166"/>
-      <c r="J26" s="166"/>
-      <c r="K26" s="166"/>
+      <c r="H26" s="165"/>
+      <c r="I26" s="165"/>
+      <c r="J26" s="165"/>
+      <c r="K26" s="165"/>
       <c r="L26" s="130"/>
       <c r="O26" s="122" t="s">
         <v>153</v>
@@ -17775,10 +17697,10 @@
       <c r="E27" s="124"/>
       <c r="F27" s="133"/>
       <c r="G27" s="133"/>
-      <c r="H27" s="166"/>
-      <c r="I27" s="166"/>
-      <c r="J27" s="166"/>
-      <c r="K27" s="166"/>
+      <c r="H27" s="165"/>
+      <c r="I27" s="165"/>
+      <c r="J27" s="165"/>
+      <c r="K27" s="165"/>
       <c r="L27" s="130"/>
       <c r="O27" s="122" t="s">
         <v>156</v>
@@ -17798,10 +17720,10 @@
       </c>
       <c r="F28" s="133"/>
       <c r="G28" s="124"/>
-      <c r="H28" s="166"/>
-      <c r="I28" s="166"/>
-      <c r="J28" s="166"/>
-      <c r="K28" s="166"/>
+      <c r="H28" s="165"/>
+      <c r="I28" s="165"/>
+      <c r="J28" s="165"/>
+      <c r="K28" s="165"/>
       <c r="L28" s="130"/>
       <c r="O28" s="122" t="s">
         <v>160</v>
@@ -17812,21 +17734,21 @@
         <v>161</v>
       </c>
       <c r="B29" s="124" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="C29" s="124" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="D29" s="131" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="E29" s="124"/>
       <c r="F29" s="124"/>
       <c r="G29" s="124"/>
-      <c r="H29" s="166"/>
-      <c r="I29" s="166"/>
-      <c r="J29" s="166"/>
-      <c r="K29" s="166"/>
+      <c r="H29" s="165"/>
+      <c r="I29" s="165"/>
+      <c r="J29" s="165"/>
+      <c r="K29" s="165"/>
       <c r="L29" s="130"/>
       <c r="O29" s="122" t="s">
         <v>123</v>
@@ -17840,18 +17762,18 @@
         <v>167</v>
       </c>
       <c r="C30" s="124" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="D30" s="124" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="E30" s="124"/>
       <c r="F30" s="124"/>
       <c r="G30" s="124"/>
-      <c r="H30" s="166"/>
-      <c r="I30" s="166"/>
-      <c r="J30" s="166"/>
-      <c r="K30" s="166"/>
+      <c r="H30" s="165"/>
+      <c r="I30" s="165"/>
+      <c r="J30" s="165"/>
+      <c r="K30" s="165"/>
       <c r="L30" s="130"/>
       <c r="O30" s="122" t="s">
         <v>76</v>
@@ -17865,18 +17787,18 @@
         <v>208</v>
       </c>
       <c r="C31" s="124" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
       <c r="D31" s="124" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
       <c r="E31" s="124"/>
       <c r="F31" s="131"/>
       <c r="G31" s="131"/>
-      <c r="H31" s="166"/>
-      <c r="I31" s="166"/>
-      <c r="J31" s="166"/>
-      <c r="K31" s="166"/>
+      <c r="H31" s="165"/>
+      <c r="I31" s="165"/>
+      <c r="J31" s="165"/>
+      <c r="K31" s="165"/>
       <c r="L31" s="130"/>
       <c r="O31" s="122" t="s">
         <v>170</v>
@@ -17887,7 +17809,7 @@
         <v>171</v>
       </c>
       <c r="B32" s="124" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
       <c r="C32" s="124" t="s">
         <v>208</v>
@@ -17971,10 +17893,10 @@
         <v>183</v>
       </c>
       <c r="B36" s="118" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="C36" s="118" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="D36" s="118"/>
       <c r="E36" s="136"/>
@@ -17990,10 +17912,10 @@
         <v>188</v>
       </c>
       <c r="B37" s="118" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="C37" s="118" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="D37" s="131"/>
       <c r="E37" s="118"/>
@@ -18013,10 +17935,10 @@
         <v>184</v>
       </c>
       <c r="D38" s="118" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="E38" s="118" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="F38" s="131"/>
       <c r="G38" s="136"/>
@@ -18036,7 +17958,7 @@
         <v>158</v>
       </c>
       <c r="D39" s="118" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="E39" s="131"/>
       <c r="F39" s="131"/>
@@ -18051,10 +17973,10 @@
         <v>196</v>
       </c>
       <c r="B40" s="118" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="C40" s="118" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="D40" s="118" t="s">
         <v>217</v>
@@ -18580,14 +18502,14 @@
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="L127" s="143"/>
-      <c r="O127" s="167" t="s">
-        <v>365</v>
+      <c r="O127" s="166" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="L128" s="143"/>
       <c r="O128" s="158" t="s">
-        <v>366</v>
+        <v>343</v>
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1">
